--- a/docs/research/Databricks_Data_Engineering_Mastery_Roadmap.xlsx
+++ b/docs/research/Databricks_Data_Engineering_Mastery_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\PrepBench\.claude\worktrees\databricks-research-1e243f\docs\research\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D771A2-9205-4096-9946-AFC171597DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34323425-181B-4317-BD98-F283F90A0AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="433">
   <si>
     <t>Phase</t>
   </si>
@@ -101,6 +101,18 @@
     <t>§17, §6.1</t>
   </si>
   <si>
+    <t>Workspace Objects and Permissions</t>
+  </si>
+  <si>
+    <t>Understand workspace-level assets (notebooks, folders, workspace files, jobs, pipelines, dashboards, queries) and that workspace access control lists, not Unity Catalog, govern them.</t>
+  </si>
+  <si>
+    <t>Sort ten objects into Unity Catalog securables and workspace assets, and say who controls access to each.</t>
+  </si>
+  <si>
+    <t>§6.1</t>
+  </si>
+  <si>
     <t>Product Names, Old and New</t>
   </si>
   <si>
@@ -488,9 +500,6 @@
     <t>Draw the hierarchy for one table, one volume and one external location, with who owns each.</t>
   </si>
   <si>
-    <t>§6.1</t>
-  </si>
-  <si>
     <t>Managed vs External Tables</t>
   </si>
   <si>
@@ -626,13 +635,22 @@
     <t>Say which access mode a shared team cluster and a single ML engineer's cluster should use.</t>
   </si>
   <si>
-    <t>Compute Policies and Pools</t>
-  </si>
-  <si>
-    <t>Understand admin compute policies that limit what users create, and pools that keep idle instances ready.</t>
-  </si>
-  <si>
-    <t>Design a policy that caps cluster size and forces auto termination for a data team.</t>
+    <t>Photon and Runtime Selection</t>
+  </si>
+  <si>
+    <t>Understand Databricks Runtime choice (latest for all-purpose, LTS for production jobs, versionless serverless) and Photon, the native vectorized engine on by default.</t>
+  </si>
+  <si>
+    <t>Choose a runtime for a production job and a development cluster, and say which workloads gain most from Photon.</t>
+  </si>
+  <si>
+    <t>Compute Policies, Pools and Autoscaling</t>
+  </si>
+  <si>
+    <t>Understand admin compute policies that limit what users create, autoscaling between minimum and maximum workers, and pools that keep idle instances ready (no DBUs while idle).</t>
+  </si>
+  <si>
+    <t>Design a policy that caps autoscaling and forces auto termination for a data team, and say when a pool is worth it.</t>
   </si>
   <si>
     <t>DBUs and Cost Levers</t>
@@ -794,16 +812,28 @@
     <t>§8, §2.7</t>
   </si>
   <si>
+    <t>Recovery, Replay and Backfill</t>
+  </si>
+  <si>
+    <t>Understand restart from a checkpoint vs starting fresh, full refresh and checkpoint reset in pipelines, RESTORE seen downstream as new data, and Auto Loader backfills.</t>
+  </si>
+  <si>
+    <t>Plan how to reprocess one bad week of data without duplicating rows downstream, naming each step's effect.</t>
+  </si>
+  <si>
+    <t>§8, §10, §2.2, §21.2</t>
+  </si>
+  <si>
     <t>10. Pipelines &amp; Orchestration</t>
   </si>
   <si>
-    <t>Streaming Tables vs Materialized Views</t>
-  </si>
-  <si>
-    <t>Master Lakeflow pipeline datasets: streaming tables (exactly-once, append-only sources) vs materialized views (recomputed to stay correct).</t>
-  </si>
-  <si>
-    <t>For five transformations, say which dataset type each should be and why.</t>
+    <t>Pipeline Datasets and Flows</t>
+  </si>
+  <si>
+    <t>Master Lakeflow pipeline datasets (streaming tables, materialized views, views) and flows (append, update, AUTO CDC, materialized view) and how dependencies form the pipeline graph.</t>
+  </si>
+  <si>
+    <t>For five transformations, say which dataset type each should be and why, and which flow writes it.</t>
   </si>
   <si>
     <t>§10</t>
@@ -857,6 +887,15 @@
     <t>Configure a cleanup task that runs even when an upstream task fails, and a retry on a flaky task.</t>
   </si>
   <si>
+    <t>Job Concurrency and Limits</t>
+  </si>
+  <si>
+    <t>Understand one run at a time by default, maximum concurrent runs (runs beyond it are skipped), and workspace limits such as 2,000 concurrent task runs.</t>
+  </si>
+  <si>
+    <t>Explain what happens when an hourly job's run takes 90 minutes, and how to change it.</t>
+  </si>
+  <si>
     <t>Triggers and Repair Runs</t>
   </si>
   <si>
@@ -875,7 +914,97 @@
     <t>Design how an ADF pipeline triggers a Databricks job and reads back its result.</t>
   </si>
   <si>
-    <t>11. Operate, Deploy &amp; Capstone</t>
+    <t>11. Azure Networking for Databricks</t>
+  </si>
+  <si>
+    <t>Three Network Connections</t>
+  </si>
+  <si>
+    <t>Understand the three connections secured separately: users to Databricks, control plane to classic compute, and serverless compute to your resources.</t>
+  </si>
+  <si>
+    <t>Draw the three connections for one workspace and name a control for each.</t>
+  </si>
+  <si>
+    <t>§20.1</t>
+  </si>
+  <si>
+    <t>Serverless vs Hybrid Workspaces</t>
+  </si>
+  <si>
+    <t>Understand serverless workspaces (default storage, serverless compute) vs hybrid (classic) workspaces in your subscription, and who may create one.</t>
+  </si>
+  <si>
+    <t>Choose a workspace type for two teams with different needs and justify it.</t>
+  </si>
+  <si>
+    <t>§20.2</t>
+  </si>
+  <si>
+    <t>VNet Injection and Subnet Sizing</t>
+  </si>
+  <si>
+    <t>Master VNet injection: same region and subscription, /16 to /24 VNet, two dedicated subnets (container and host, /26 recommended), two IPs per node, ranges fixed after deployment.</t>
+  </si>
+  <si>
+    <t>Size a VNet and its two subnets for a 100-node peak and show the arithmetic.</t>
+  </si>
+  <si>
+    <t>§20.3</t>
+  </si>
+  <si>
+    <t>Subnet Delegation and NSG Rules</t>
+  </si>
+  <si>
+    <t>Understand subnet delegation to Databricks, the managed NSG rules and their ports, and why they must not be modified.</t>
+  </si>
+  <si>
+    <t>Explain which outbound ports a VNet-injected workspace needs and what each one is for.</t>
+  </si>
+  <si>
+    <t>Secure Cluster Connectivity and Egress</t>
+  </si>
+  <si>
+    <t>Master secure cluster connectivity (no public IPs, outbound relay on 443), NAT gateway egress, and the March 2026 change to default outbound access.</t>
+  </si>
+  <si>
+    <t>Explain why a new workspace's clusters can't reach the internet without a NAT gateway, and how to fix it.</t>
+  </si>
+  <si>
+    <t>§20.4</t>
+  </si>
+  <si>
+    <t>Private Link: Three Kinds</t>
+  </si>
+  <si>
+    <t>Understand inbound (front-end), outbound (serverless) and classic (back-end) Private Link, their prerequisites and endpoints, and complete private isolation.</t>
+  </si>
+  <si>
+    <t>Pick the Private Link setup for a bank that forbids any public path, and list the endpoints it needs.</t>
+  </si>
+  <si>
+    <t>§20.5</t>
+  </si>
+  <si>
+    <t>Browser Authentication and the Transit VNet</t>
+  </si>
+  <si>
+    <t>Understand the browser_authentication endpoint (one per region and DNS zone), the private web auth workspace, and transit vs workspace VNets.</t>
+  </si>
+  <si>
+    <t>Explain why deleting one workspace could break SSO for every private workspace in the region.</t>
+  </si>
+  <si>
+    <t>Serverless Connectivity and Storage Firewalls</t>
+  </si>
+  <si>
+    <t>Understand NCCs and serverless private endpoints, service endpoints, and storage firewalls with network security perimeters and the AzureDatabricksServerless tag.</t>
+  </si>
+  <si>
+    <t>Diagnose a serverless job getting 403 Forbidden from a firewalled ADLS account and give the fix.</t>
+  </si>
+  <si>
+    <t>12. Operate, Deploy &amp; Capstone</t>
   </si>
   <si>
     <t>System Tables and Monitoring</t>
@@ -944,7 +1073,7 @@
     <t>Run the pipeline in Free Edition, grant a reader group on gold, and explain every design choice to a reviewer.</t>
   </si>
   <si>
-    <t>1-22</t>
+    <t>1-23</t>
   </si>
   <si>
     <t>all</t>
@@ -1586,7 +1715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1701,7 +1830,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="56" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -1727,7 +1856,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="56" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1744,7 +1873,7 @@
         <v>27</v>
       </c>
       <c r="F6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -1753,35 +1882,35 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="B7" s="3">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="F7" s="3">
         <v>2</v>
       </c>
       <c r="G7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="42" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
@@ -1796,7 +1925,7 @@
         <v>36</v>
       </c>
       <c r="F8" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="2">
         <v>2</v>
@@ -1805,9 +1934,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
@@ -1831,9 +1960,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
@@ -1859,7 +1988,7 @@
     </row>
     <row r="11" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
@@ -1874,7 +2003,7 @@
         <v>48</v>
       </c>
       <c r="F11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="3">
         <v>2</v>
@@ -1885,7 +2014,7 @@
     </row>
     <row r="12" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B12" s="2">
         <v>11</v>
@@ -1906,12 +2035,12 @@
         <v>2</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="B13" s="3">
         <v>12</v>
@@ -1929,15 +2058,15 @@
         <v>2</v>
       </c>
       <c r="G13" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="42" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="B14" s="2">
         <v>13</v>
@@ -1952,30 +2081,30 @@
         <v>60</v>
       </c>
       <c r="F14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" s="2">
         <v>3</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B15" s="3">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F15" s="3">
         <v>3</v>
@@ -1984,12 +2113,12 @@
         <v>3</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B16" s="2">
         <v>15</v>
@@ -2013,9 +2142,9 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B17" s="3">
         <v>16</v>
@@ -2041,7 +2170,7 @@
     </row>
     <row r="18" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B18" s="2">
         <v>17</v>
@@ -2056,70 +2185,70 @@
         <v>75</v>
       </c>
       <c r="F18" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="2">
         <v>3</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B19" s="3">
         <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F19" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19" s="3">
         <v>3</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B20" s="2">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F20" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="2">
         <v>3</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B21" s="3">
         <v>20</v>
@@ -2145,33 +2274,33 @@
     </row>
     <row r="22" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="B22" s="2">
         <v>21</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2">
+        <v>3</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="F22" s="2">
-        <v>1</v>
-      </c>
-      <c r="G22" s="2">
-        <v>4</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B23" s="3">
         <v>22</v>
@@ -2186,30 +2315,30 @@
         <v>94</v>
       </c>
       <c r="F23" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="3">
         <v>4</v>
       </c>
       <c r="H23" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="42" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="B24" s="2">
         <v>23</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F24" s="2">
         <v>2</v>
@@ -2218,24 +2347,24 @@
         <v>4</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B25" s="3">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F25" s="3">
         <v>2</v>
@@ -2244,12 +2373,12 @@
         <v>4</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B26" s="2">
         <v>25</v>
@@ -2270,38 +2399,38 @@
         <v>4</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="28" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="B27" s="3">
         <v>26</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F27" s="3">
         <v>2</v>
       </c>
       <c r="G27" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B28" s="2">
         <v>27</v>
@@ -2322,38 +2451,38 @@
         <v>5</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B29" s="3">
         <v>28</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F29" s="3">
+        <v>2</v>
+      </c>
+      <c r="G29" s="3">
+        <v>5</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F29" s="3">
-        <v>4</v>
-      </c>
-      <c r="G29" s="3">
-        <v>6</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B30" s="2">
         <v>29</v>
@@ -2368,7 +2497,7 @@
         <v>118</v>
       </c>
       <c r="F30" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" s="2">
         <v>6</v>
@@ -2379,33 +2508,33 @@
     </row>
     <row r="31" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="B31" s="3">
         <v>30</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3">
+        <v>3</v>
+      </c>
+      <c r="G31" s="3">
+        <v>6</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="F31" s="3">
-        <v>2</v>
-      </c>
-      <c r="G31" s="3">
-        <v>7</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B32" s="2">
         <v>31</v>
@@ -2431,7 +2560,7 @@
     </row>
     <row r="33" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B33" s="3">
         <v>32</v>
@@ -2452,90 +2581,90 @@
         <v>7</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B34" s="2">
         <v>33</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F34" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G34" s="2">
         <v>7</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B35" s="3">
         <v>34</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F35" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" s="3">
         <v>7</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B36" s="2">
         <v>35</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" s="2">
         <v>7</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B37" s="3">
         <v>36</v>
@@ -2550,7 +2679,7 @@
         <v>144</v>
       </c>
       <c r="F37" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" s="3">
         <v>7</v>
@@ -2561,33 +2690,33 @@
     </row>
     <row r="38" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="B38" s="2">
         <v>37</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="F38" s="2">
         <v>2</v>
       </c>
       <c r="G38" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H38" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
         <v>150</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="28" x14ac:dyDescent="0.35">
-      <c r="A39" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="B39" s="3">
         <v>38</v>
@@ -2602,174 +2731,174 @@
         <v>153</v>
       </c>
       <c r="F39" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G39" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>154</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B40" s="2">
         <v>39</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>157</v>
-      </c>
       <c r="F40" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G40" s="2">
         <v>9</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B41" s="3">
         <v>40</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="E41" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="F41" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G41" s="3">
         <v>9</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B42" s="2">
         <v>41</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="E42" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="F42" s="2">
         <v>3</v>
       </c>
       <c r="G42" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B43" s="3">
         <v>42</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="E43" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="F43" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43" s="3">
         <v>10</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B44" s="2">
         <v>43</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>173</v>
-      </c>
       <c r="F44" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G44" s="2">
         <v>10</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B45" s="3">
         <v>44</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="F45" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45" s="3">
         <v>10</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B46" s="2">
         <v>45</v>
@@ -2790,64 +2919,64 @@
         <v>10</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="B47" s="3">
         <v>46</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="F47" s="3">
         <v>2</v>
       </c>
       <c r="G47" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B48" s="2">
         <v>47</v>
       </c>
       <c r="C48" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="E48" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="F48" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" s="2">
         <v>11</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B49" s="3">
         <v>48</v>
@@ -2868,12 +2997,12 @@
         <v>11</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B50" s="2">
         <v>49</v>
@@ -2894,12 +3023,12 @@
         <v>11</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B51" s="3">
         <v>50</v>
@@ -2914,18 +3043,18 @@
         <v>198</v>
       </c>
       <c r="F51" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" s="3">
         <v>11</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B52" s="2">
         <v>51</v>
@@ -2946,76 +3075,76 @@
         <v>11</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="B53" s="3">
         <v>52</v>
       </c>
       <c r="C53" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="E53" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="F53" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G53" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="B54" s="2">
         <v>53</v>
       </c>
       <c r="C54" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="F54" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G54" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B55" s="3">
         <v>54</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="E55" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="F55" s="3">
         <v>3</v>
@@ -3024,12 +3153,12 @@
         <v>12</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B56" s="2">
         <v>55</v>
@@ -3047,15 +3176,15 @@
         <v>3</v>
       </c>
       <c r="G56" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B57" s="3">
         <v>56</v>
@@ -3073,15 +3202,15 @@
         <v>3</v>
       </c>
       <c r="G57" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B58" s="2">
         <v>57</v>
@@ -3099,15 +3228,15 @@
         <v>3</v>
       </c>
       <c r="G58" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B59" s="3">
         <v>58</v>
@@ -3122,186 +3251,186 @@
         <v>224</v>
       </c>
       <c r="F59" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G59" s="3">
         <v>19</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="B60" s="2">
         <v>59</v>
       </c>
       <c r="C60" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="F60" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G60" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="B61" s="3">
         <v>60</v>
       </c>
       <c r="C61" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E61" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="F61" s="3">
         <v>2</v>
       </c>
       <c r="G61" s="3">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B62" s="2">
         <v>61</v>
       </c>
       <c r="C62" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="F62" s="2">
+        <v>2</v>
+      </c>
+      <c r="G62" s="2">
+        <v>14</v>
+      </c>
+      <c r="H62" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F62" s="2">
-        <v>3</v>
-      </c>
-      <c r="G62" s="2">
-        <v>15</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+    </row>
+    <row r="63" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B63" s="3">
         <v>62</v>
       </c>
       <c r="C63" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="F63" s="3">
+        <v>2</v>
+      </c>
+      <c r="G63" s="3">
+        <v>14</v>
+      </c>
+      <c r="H63" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="E63" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="F63" s="3">
-        <v>3</v>
-      </c>
-      <c r="G63" s="3">
-        <v>15</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+    </row>
+    <row r="64" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B64" s="2">
         <v>63</v>
       </c>
       <c r="C64" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="E64" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="F64" s="2">
         <v>3</v>
       </c>
       <c r="G64" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B65" s="3">
         <v>64</v>
       </c>
       <c r="C65" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="E65" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="F65" s="3">
         <v>3</v>
       </c>
       <c r="G65" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B66" s="2">
         <v>65</v>
       </c>
       <c r="C66" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="E66" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>250</v>
       </c>
       <c r="F66" s="2">
         <v>3</v>
@@ -3310,90 +3439,90 @@
         <v>16</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="B67" s="3">
         <v>66</v>
       </c>
       <c r="C67" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>255</v>
       </c>
       <c r="F67" s="3">
         <v>3</v>
       </c>
       <c r="G67" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="B68" s="2">
         <v>67</v>
       </c>
       <c r="C68" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F68" s="2">
+        <v>3</v>
+      </c>
+      <c r="G68" s="2">
+        <v>16</v>
+      </c>
+      <c r="H68" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F68" s="2">
-        <v>2</v>
-      </c>
-      <c r="G68" s="2">
-        <v>17</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+    </row>
+    <row r="69" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="B69" s="3">
         <v>68</v>
       </c>
       <c r="C69" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>260</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>262</v>
       </c>
       <c r="F69" s="3">
         <v>3</v>
       </c>
       <c r="G69" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B70" s="2">
         <v>69</v>
@@ -3408,44 +3537,44 @@
         <v>265</v>
       </c>
       <c r="F70" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G70" s="2">
         <v>17</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B71" s="3">
         <v>70</v>
       </c>
       <c r="C71" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F71" s="3">
+        <v>2</v>
+      </c>
+      <c r="G71" s="3">
+        <v>17</v>
+      </c>
+      <c r="H71" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="F71" s="3">
-        <v>3</v>
-      </c>
-      <c r="G71" s="3">
-        <v>18</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B72" s="2">
         <v>71</v>
@@ -3460,18 +3589,18 @@
         <v>272</v>
       </c>
       <c r="F72" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G72" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B73" s="3">
         <v>72</v>
@@ -3489,15 +3618,15 @@
         <v>2</v>
       </c>
       <c r="G73" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B74" s="2">
         <v>73</v>
@@ -3512,18 +3641,18 @@
         <v>278</v>
       </c>
       <c r="F74" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G74" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>16</v>
+        <v>279</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="B75" s="3">
         <v>74</v>
@@ -3538,152 +3667,464 @@
         <v>282</v>
       </c>
       <c r="F75" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G75" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="B76" s="2">
         <v>75</v>
       </c>
       <c r="C76" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D76" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="E76" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>286</v>
-      </c>
       <c r="F76" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G76" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="B77" s="3">
         <v>76</v>
       </c>
       <c r="C77" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>288</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>290</v>
       </c>
       <c r="F77" s="3">
         <v>2</v>
       </c>
       <c r="G77" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="B78" s="2">
         <v>77</v>
       </c>
       <c r="C78" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F78" s="2">
+        <v>2</v>
+      </c>
+      <c r="G78" s="2">
+        <v>22</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A79" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F78" s="2">
-        <v>1</v>
-      </c>
-      <c r="G78" s="2">
-        <v>21</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="28" x14ac:dyDescent="0.35">
-      <c r="A79" s="3" t="s">
-        <v>279</v>
       </c>
       <c r="B79" s="3">
         <v>78</v>
       </c>
       <c r="C79" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="F79" s="3">
+        <v>2</v>
+      </c>
+      <c r="G79" s="3">
+        <v>23</v>
+      </c>
+      <c r="H79" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="F79" s="3">
-        <v>4</v>
-      </c>
-      <c r="G79" s="3">
-        <v>21</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+    </row>
+    <row r="80" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="B80" s="2">
         <v>79</v>
       </c>
       <c r="C80" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="F80" s="2">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2">
+        <v>23</v>
+      </c>
+      <c r="H80" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="E80" s="2" t="s">
+    </row>
+    <row r="81" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A81" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B81" s="3">
+        <v>80</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="F80" s="2">
+      <c r="D81" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F81" s="3">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3">
+        <v>23</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A82" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B82" s="2">
+        <v>81</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F82" s="2">
+        <v>2</v>
+      </c>
+      <c r="G82" s="2">
+        <v>23</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A83" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B83" s="3">
+        <v>82</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F83" s="3">
+        <v>2</v>
+      </c>
+      <c r="G83" s="3">
+        <v>23</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A84" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B84" s="2">
+        <v>83</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F84" s="2">
+        <v>3</v>
+      </c>
+      <c r="G84" s="2">
+        <v>23</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A85" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B85" s="3">
+        <v>84</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F85" s="3">
+        <v>2</v>
+      </c>
+      <c r="G85" s="3">
+        <v>23</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A86" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B86" s="2">
+        <v>85</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F86" s="2">
+        <v>2</v>
+      </c>
+      <c r="G86" s="2">
+        <v>23</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A87" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B87" s="3">
+        <v>86</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F87" s="3">
+        <v>3</v>
+      </c>
+      <c r="G87" s="3">
+        <v>20</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A88" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B88" s="2">
+        <v>87</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="F88" s="2">
+        <v>2</v>
+      </c>
+      <c r="G88" s="2">
+        <v>20</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A89" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B89" s="3">
+        <v>88</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="F89" s="3">
+        <v>2</v>
+      </c>
+      <c r="G89" s="3">
+        <v>21</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A90" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B90" s="2">
+        <v>89</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F90" s="2">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2">
+        <v>21</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A91" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B91" s="3">
+        <v>90</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F91" s="3">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3">
+        <v>21</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A92" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B92" s="2">
+        <v>91</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F92" s="2">
         <v>10</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="81" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C81" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="F81" s="4">
-        <f>SUM(F2:F80)</f>
-        <v>193</v>
+      <c r="G92" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C93" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="F93" s="4">
+        <f>SUM(F2:F92)</f>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -3693,7 +4134,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3707,45 +4148,45 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>305</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>306</v>
+        <v>349</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>307</v>
+        <v>350</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>308</v>
+        <v>351</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>310</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
-        <f>COUNTA(B6:B84)</f>
-        <v>79</v>
+        <f>COUNTA(B6:B96)</f>
+        <v>91</v>
       </c>
       <c r="B3" s="5">
-        <f>COUNTIF(D6:D84,"Completed")</f>
+        <f>COUNTIF(D6:D96,"Completed")</f>
         <v>0</v>
       </c>
       <c r="C3" s="5">
-        <f>COUNTIF(D6:D84,"In Progress")</f>
+        <f>COUNTIF(D6:D96,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="D3" s="5">
-        <f>COUNTIF(D6:D84,"Not Started")</f>
-        <v>79</v>
+        <f>COUNTIF(D6:D96,"Not Started")</f>
+        <v>91</v>
       </c>
       <c r="E3" s="6">
-        <f>AVERAGE(E6:E84)/100</f>
+        <f>AVERAGE(E6:E96)/100</f>
         <v>0</v>
       </c>
     </row>
@@ -3760,19 +4201,19 @@
         <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>311</v>
+        <v>354</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>312</v>
+        <v>355</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>313</v>
+        <v>356</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>314</v>
+        <v>357</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>315</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -3788,7 +4229,7 @@
         <v>1. Lakehouse &amp; Platform Foundations</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
@@ -3810,7 +4251,7 @@
         <v>1. Lakehouse &amp; Platform Foundations</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
@@ -3832,7 +4273,7 @@
         <v>1. Lakehouse &amp; Platform Foundations</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
@@ -3847,14 +4288,14 @@
       </c>
       <c r="B9" s="3" t="str">
         <f>'Databricks Master Syllabus'!C5</f>
-        <v>Product Names, Old and New</v>
+        <v>Workspace Objects and Permissions</v>
       </c>
       <c r="C9" s="3" t="str">
         <f>'Databricks Master Syllabus'!A5</f>
         <v>1. Lakehouse &amp; Platform Foundations</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
@@ -3869,14 +4310,14 @@
       </c>
       <c r="B10" s="2" t="str">
         <f>'Databricks Master Syllabus'!C6</f>
-        <v>Databricks Free Edition Setup</v>
+        <v>Product Names, Old and New</v>
       </c>
       <c r="C10" s="2" t="str">
         <f>'Databricks Master Syllabus'!A6</f>
         <v>1. Lakehouse &amp; Platform Foundations</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E10" s="2">
         <v>0</v>
@@ -3891,14 +4332,14 @@
       </c>
       <c r="B11" s="3" t="str">
         <f>'Databricks Master Syllabus'!C7</f>
-        <v>Columnar Storage</v>
+        <v>Databricks Free Edition Setup</v>
       </c>
       <c r="C11" s="3" t="str">
         <f>'Databricks Master Syllabus'!A7</f>
-        <v>2. Parquet: The File Format</v>
+        <v>1. Lakehouse &amp; Platform Foundations</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E11" s="3">
         <v>0</v>
@@ -3913,14 +4354,14 @@
       </c>
       <c r="B12" s="2" t="str">
         <f>'Databricks Master Syllabus'!C8</f>
-        <v>Parquet File Anatomy</v>
+        <v>Columnar Storage</v>
       </c>
       <c r="C12" s="2" t="str">
         <f>'Databricks Master Syllabus'!A8</f>
         <v>2. Parquet: The File Format</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E12" s="2">
         <v>0</v>
@@ -3935,14 +4376,14 @@
       </c>
       <c r="B13" s="3" t="str">
         <f>'Databricks Master Syllabus'!C9</f>
-        <v>Statistics, Page Index and Bloom Filters</v>
+        <v>Parquet File Anatomy</v>
       </c>
       <c r="C13" s="3" t="str">
         <f>'Databricks Master Syllabus'!A9</f>
         <v>2. Parquet: The File Format</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E13" s="3">
         <v>0</v>
@@ -3957,14 +4398,14 @@
       </c>
       <c r="B14" s="2" t="str">
         <f>'Databricks Master Syllabus'!C10</f>
-        <v>Types, Encodings and Compression</v>
+        <v>Statistics, Page Index and Bloom Filters</v>
       </c>
       <c r="C14" s="2" t="str">
         <f>'Databricks Master Syllabus'!A10</f>
         <v>2. Parquet: The File Format</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -3979,14 +4420,14 @@
       </c>
       <c r="B15" s="3" t="str">
         <f>'Databricks Master Syllabus'!C11</f>
-        <v>Parquet in Spark</v>
+        <v>Types, Encodings and Compression</v>
       </c>
       <c r="C15" s="3" t="str">
         <f>'Databricks Master Syllabus'!A11</f>
         <v>2. Parquet: The File Format</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -4001,14 +4442,14 @@
       </c>
       <c r="B16" s="2" t="str">
         <f>'Databricks Master Syllabus'!C12</f>
-        <v>Hive-Style Partitioning and Small Files</v>
+        <v>Parquet in Spark</v>
       </c>
       <c r="C16" s="2" t="str">
         <f>'Databricks Master Syllabus'!A12</f>
         <v>2. Parquet: The File Format</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
@@ -4023,14 +4464,14 @@
       </c>
       <c r="B17" s="3" t="str">
         <f>'Databricks Master Syllabus'!C13</f>
-        <v>Delta Lake = Parquet + Transaction Log</v>
+        <v>Hive-Style Partitioning and Small Files</v>
       </c>
       <c r="C17" s="3" t="str">
         <f>'Databricks Master Syllabus'!A13</f>
-        <v>3. Delta Lake Internals</v>
+        <v>2. Parquet: The File Format</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
@@ -4045,14 +4486,14 @@
       </c>
       <c r="B18" s="2" t="str">
         <f>'Databricks Master Syllabus'!C14</f>
-        <v>Commit Files in _delta_log</v>
+        <v>Delta Lake = Parquet + Transaction Log</v>
       </c>
       <c r="C18" s="2" t="str">
         <f>'Databricks Master Syllabus'!A14</f>
         <v>3. Delta Lake Internals</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E18" s="2">
         <v>0</v>
@@ -4067,14 +4508,14 @@
       </c>
       <c r="B19" s="3" t="str">
         <f>'Databricks Master Syllabus'!C15</f>
-        <v>Log Actions</v>
+        <v>Commit Files in _delta_log</v>
       </c>
       <c r="C19" s="3" t="str">
         <f>'Databricks Master Syllabus'!A15</f>
         <v>3. Delta Lake Internals</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E19" s="3">
         <v>0</v>
@@ -4089,14 +4530,14 @@
       </c>
       <c r="B20" s="2" t="str">
         <f>'Databricks Master Syllabus'!C16</f>
-        <v>Snapshots, Tombstones and Log Replay</v>
+        <v>Log Actions</v>
       </c>
       <c r="C20" s="2" t="str">
         <f>'Databricks Master Syllabus'!A16</f>
         <v>3. Delta Lake Internals</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E20" s="2">
         <v>0</v>
@@ -4111,14 +4552,14 @@
       </c>
       <c r="B21" s="3" t="str">
         <f>'Databricks Master Syllabus'!C17</f>
-        <v>Checkpoints and _last_checkpoint</v>
+        <v>Snapshots, Tombstones and Log Replay</v>
       </c>
       <c r="C21" s="3" t="str">
         <f>'Databricks Master Syllabus'!A17</f>
         <v>3. Delta Lake Internals</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E21" s="3">
         <v>0</v>
@@ -4133,14 +4574,14 @@
       </c>
       <c r="B22" s="2" t="str">
         <f>'Databricks Master Syllabus'!C18</f>
-        <v>Optimistic Concurrency and Write Conflicts</v>
+        <v>Checkpoints and _last_checkpoint</v>
       </c>
       <c r="C22" s="2" t="str">
         <f>'Databricks Master Syllabus'!A18</f>
         <v>3. Delta Lake Internals</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
@@ -4155,14 +4596,14 @@
       </c>
       <c r="B23" s="3" t="str">
         <f>'Databricks Master Syllabus'!C19</f>
-        <v>Isolation Levels and Transaction Scope</v>
+        <v>Optimistic Concurrency and Write Conflicts</v>
       </c>
       <c r="C23" s="3" t="str">
         <f>'Databricks Master Syllabus'!A19</f>
         <v>3. Delta Lake Internals</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
@@ -4177,14 +4618,14 @@
       </c>
       <c r="B24" s="2" t="str">
         <f>'Databricks Master Syllabus'!C20</f>
-        <v>Protocol Versions and Table Features</v>
+        <v>Isolation Levels and Transaction Scope</v>
       </c>
       <c r="C24" s="2" t="str">
         <f>'Databricks Master Syllabus'!A20</f>
         <v>3. Delta Lake Internals</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E24" s="2">
         <v>0</v>
@@ -4199,14 +4640,14 @@
       </c>
       <c r="B25" s="3" t="str">
         <f>'Databricks Master Syllabus'!C21</f>
-        <v>Idempotent Writes with Transaction Identifiers</v>
+        <v>Protocol Versions and Table Features</v>
       </c>
       <c r="C25" s="3" t="str">
         <f>'Databricks Master Syllabus'!A21</f>
         <v>3. Delta Lake Internals</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E25" s="3">
         <v>0</v>
@@ -4221,14 +4662,14 @@
       </c>
       <c r="B26" s="2" t="str">
         <f>'Databricks Master Syllabus'!C22</f>
-        <v>Table History</v>
+        <v>Idempotent Writes with Transaction Identifiers</v>
       </c>
       <c r="C26" s="2" t="str">
         <f>'Databricks Master Syllabus'!A22</f>
-        <v>4. Delta Lake Operations</v>
+        <v>3. Delta Lake Internals</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E26" s="2">
         <v>0</v>
@@ -4243,14 +4684,14 @@
       </c>
       <c r="B27" s="3" t="str">
         <f>'Databricks Master Syllabus'!C23</f>
-        <v>Time Travel</v>
+        <v>Table History</v>
       </c>
       <c r="C27" s="3" t="str">
         <f>'Databricks Master Syllabus'!A23</f>
         <v>4. Delta Lake Operations</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E27" s="3">
         <v>0</v>
@@ -4265,14 +4706,14 @@
       </c>
       <c r="B28" s="2" t="str">
         <f>'Databricks Master Syllabus'!C24</f>
-        <v>Log Retention vs Deleted-File Retention</v>
+        <v>Time Travel</v>
       </c>
       <c r="C28" s="2" t="str">
         <f>'Databricks Master Syllabus'!A24</f>
         <v>4. Delta Lake Operations</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E28" s="2">
         <v>0</v>
@@ -4287,14 +4728,14 @@
       </c>
       <c r="B29" s="3" t="str">
         <f>'Databricks Master Syllabus'!C25</f>
-        <v>VACUUM</v>
+        <v>Log Retention vs Deleted-File Retention</v>
       </c>
       <c r="C29" s="3" t="str">
         <f>'Databricks Master Syllabus'!A25</f>
         <v>4. Delta Lake Operations</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -4309,14 +4750,14 @@
       </c>
       <c r="B30" s="2" t="str">
         <f>'Databricks Master Syllabus'!C26</f>
-        <v>RESTORE</v>
+        <v>VACUUM</v>
       </c>
       <c r="C30" s="2" t="str">
         <f>'Databricks Master Syllabus'!A26</f>
         <v>4. Delta Lake Operations</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E30" s="2">
         <v>0</v>
@@ -4331,14 +4772,14 @@
       </c>
       <c r="B31" s="3" t="str">
         <f>'Databricks Master Syllabus'!C27</f>
-        <v>Schema Enforcement</v>
+        <v>RESTORE</v>
       </c>
       <c r="C31" s="3" t="str">
         <f>'Databricks Master Syllabus'!A27</f>
         <v>4. Delta Lake Operations</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E31" s="3">
         <v>0</v>
@@ -4353,14 +4794,14 @@
       </c>
       <c r="B32" s="2" t="str">
         <f>'Databricks Master Syllabus'!C28</f>
-        <v>Schema Evolution</v>
+        <v>Schema Enforcement</v>
       </c>
       <c r="C32" s="2" t="str">
         <f>'Databricks Master Syllabus'!A28</f>
         <v>4. Delta Lake Operations</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E32" s="2">
         <v>0</v>
@@ -4375,14 +4816,14 @@
       </c>
       <c r="B33" s="3" t="str">
         <f>'Databricks Master Syllabus'!C29</f>
-        <v>MERGE Upserts</v>
+        <v>Schema Evolution</v>
       </c>
       <c r="C33" s="3" t="str">
         <f>'Databricks Master Syllabus'!A29</f>
         <v>4. Delta Lake Operations</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E33" s="3">
         <v>0</v>
@@ -4397,14 +4838,14 @@
       </c>
       <c r="B34" s="2" t="str">
         <f>'Databricks Master Syllabus'!C30</f>
-        <v>Change Data Feed</v>
+        <v>MERGE Upserts</v>
       </c>
       <c r="C34" s="2" t="str">
         <f>'Databricks Master Syllabus'!A30</f>
         <v>4. Delta Lake Operations</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E34" s="2">
         <v>0</v>
@@ -4419,14 +4860,14 @@
       </c>
       <c r="B35" s="3" t="str">
         <f>'Databricks Master Syllabus'!C31</f>
-        <v>OPTIMIZE and Compaction</v>
+        <v>Change Data Feed</v>
       </c>
       <c r="C35" s="3" t="str">
         <f>'Databricks Master Syllabus'!A31</f>
-        <v>5. Data Layout &amp; Table Optimization</v>
+        <v>4. Delta Lake Operations</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E35" s="3">
         <v>0</v>
@@ -4441,14 +4882,14 @@
       </c>
       <c r="B36" s="2" t="str">
         <f>'Databricks Master Syllabus'!C32</f>
-        <v>Data Skipping and File Statistics</v>
+        <v>OPTIMIZE and Compaction</v>
       </c>
       <c r="C36" s="2" t="str">
         <f>'Databricks Master Syllabus'!A32</f>
         <v>5. Data Layout &amp; Table Optimization</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E36" s="2">
         <v>0</v>
@@ -4463,14 +4904,14 @@
       </c>
       <c r="B37" s="3" t="str">
         <f>'Databricks Master Syllabus'!C33</f>
-        <v>Z-Order</v>
+        <v>Data Skipping and File Statistics</v>
       </c>
       <c r="C37" s="3" t="str">
         <f>'Databricks Master Syllabus'!A33</f>
         <v>5. Data Layout &amp; Table Optimization</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E37" s="3">
         <v>0</v>
@@ -4485,14 +4926,14 @@
       </c>
       <c r="B38" s="2" t="str">
         <f>'Databricks Master Syllabus'!C34</f>
-        <v>Liquid Clustering</v>
+        <v>Z-Order</v>
       </c>
       <c r="C38" s="2" t="str">
         <f>'Databricks Master Syllabus'!A34</f>
         <v>5. Data Layout &amp; Table Optimization</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E38" s="2">
         <v>0</v>
@@ -4507,14 +4948,14 @@
       </c>
       <c r="B39" s="3" t="str">
         <f>'Databricks Master Syllabus'!C35</f>
-        <v>Deletion Vectors</v>
+        <v>Liquid Clustering</v>
       </c>
       <c r="C39" s="3" t="str">
         <f>'Databricks Master Syllabus'!A35</f>
         <v>5. Data Layout &amp; Table Optimization</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E39" s="3">
         <v>0</v>
@@ -4529,14 +4970,14 @@
       </c>
       <c r="B40" s="2" t="str">
         <f>'Databricks Master Syllabus'!C36</f>
-        <v>Predictive Optimization</v>
+        <v>Deletion Vectors</v>
       </c>
       <c r="C40" s="2" t="str">
         <f>'Databricks Master Syllabus'!A36</f>
         <v>5. Data Layout &amp; Table Optimization</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E40" s="2">
         <v>0</v>
@@ -4551,14 +4992,14 @@
       </c>
       <c r="B41" s="3" t="str">
         <f>'Databricks Master Syllabus'!C37</f>
-        <v>Partitioning on Databricks</v>
+        <v>Predictive Optimization</v>
       </c>
       <c r="C41" s="3" t="str">
         <f>'Databricks Master Syllabus'!A37</f>
         <v>5. Data Layout &amp; Table Optimization</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E41" s="3">
         <v>0</v>
@@ -4573,14 +5014,14 @@
       </c>
       <c r="B42" s="2" t="str">
         <f>'Databricks Master Syllabus'!C38</f>
-        <v>Unity Catalog Object Model</v>
+        <v>Partitioning on Databricks</v>
       </c>
       <c r="C42" s="2" t="str">
         <f>'Databricks Master Syllabus'!A38</f>
-        <v>6. Unity Catalog &amp; Governance</v>
+        <v>5. Data Layout &amp; Table Optimization</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E42" s="2">
         <v>0</v>
@@ -4595,14 +5036,14 @@
       </c>
       <c r="B43" s="3" t="str">
         <f>'Databricks Master Syllabus'!C39</f>
-        <v>Managed vs External Tables</v>
+        <v>Unity Catalog Object Model</v>
       </c>
       <c r="C43" s="3" t="str">
         <f>'Databricks Master Syllabus'!A39</f>
         <v>6. Unity Catalog &amp; Governance</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
@@ -4617,14 +5058,14 @@
       </c>
       <c r="B44" s="2" t="str">
         <f>'Databricks Master Syllabus'!C40</f>
-        <v>Volumes</v>
+        <v>Managed vs External Tables</v>
       </c>
       <c r="C44" s="2" t="str">
         <f>'Databricks Master Syllabus'!A40</f>
         <v>6. Unity Catalog &amp; Governance</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E44" s="2">
         <v>0</v>
@@ -4633,20 +5074,20 @@
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
     </row>
-    <row r="45" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>40</v>
       </c>
       <c r="B45" s="3" t="str">
         <f>'Databricks Master Syllabus'!C41</f>
-        <v>Storage Credentials and External Locations on Azure</v>
+        <v>Volumes</v>
       </c>
       <c r="C45" s="3" t="str">
         <f>'Databricks Master Syllabus'!A41</f>
         <v>6. Unity Catalog &amp; Governance</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
@@ -4655,20 +5096,20 @@
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>41</v>
       </c>
       <c r="B46" s="2" t="str">
         <f>'Databricks Master Syllabus'!C42</f>
-        <v>Privileges and Inheritance</v>
+        <v>Storage Credentials and External Locations on Azure</v>
       </c>
       <c r="C46" s="2" t="str">
         <f>'Databricks Master Syllabus'!A42</f>
         <v>6. Unity Catalog &amp; Governance</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E46" s="2">
         <v>0</v>
@@ -4683,14 +5124,14 @@
       </c>
       <c r="B47" s="3" t="str">
         <f>'Databricks Master Syllabus'!C43</f>
-        <v>Ownership and the Missing DENY</v>
+        <v>Privileges and Inheritance</v>
       </c>
       <c r="C47" s="3" t="str">
         <f>'Databricks Master Syllabus'!A43</f>
         <v>6. Unity Catalog &amp; Governance</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E47" s="3">
         <v>0</v>
@@ -4705,14 +5146,14 @@
       </c>
       <c r="B48" s="2" t="str">
         <f>'Databricks Master Syllabus'!C44</f>
-        <v>Row Filters and Column Masks</v>
+        <v>Ownership and the Missing DENY</v>
       </c>
       <c r="C48" s="2" t="str">
         <f>'Databricks Master Syllabus'!A44</f>
         <v>6. Unity Catalog &amp; Governance</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E48" s="2">
         <v>0</v>
@@ -4727,14 +5168,14 @@
       </c>
       <c r="B49" s="3" t="str">
         <f>'Databricks Master Syllabus'!C45</f>
-        <v>ABAC and Dynamic Views</v>
+        <v>Row Filters and Column Masks</v>
       </c>
       <c r="C49" s="3" t="str">
         <f>'Databricks Master Syllabus'!A45</f>
         <v>6. Unity Catalog &amp; Governance</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -4749,14 +5190,14 @@
       </c>
       <c r="B50" s="2" t="str">
         <f>'Databricks Master Syllabus'!C46</f>
-        <v>Lineage and Audit</v>
+        <v>ABAC and Dynamic Views</v>
       </c>
       <c r="C50" s="2" t="str">
         <f>'Databricks Master Syllabus'!A46</f>
         <v>6. Unity Catalog &amp; Governance</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E50" s="2">
         <v>0</v>
@@ -4771,14 +5212,14 @@
       </c>
       <c r="B51" s="3" t="str">
         <f>'Databricks Master Syllabus'!C47</f>
-        <v>Serverless vs Classic Compute</v>
+        <v>Lineage and Audit</v>
       </c>
       <c r="C51" s="3" t="str">
         <f>'Databricks Master Syllabus'!A47</f>
-        <v>7. Compute &amp; Cost</v>
+        <v>6. Unity Catalog &amp; Governance</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E51" s="3">
         <v>0</v>
@@ -4793,14 +5234,14 @@
       </c>
       <c r="B52" s="2" t="str">
         <f>'Databricks Master Syllabus'!C48</f>
-        <v>All-Purpose vs Job Compute</v>
+        <v>Serverless vs Classic Compute</v>
       </c>
       <c r="C52" s="2" t="str">
         <f>'Databricks Master Syllabus'!A48</f>
         <v>7. Compute &amp; Cost</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E52" s="2">
         <v>0</v>
@@ -4815,14 +5256,14 @@
       </c>
       <c r="B53" s="3" t="str">
         <f>'Databricks Master Syllabus'!C49</f>
-        <v>SQL Warehouses</v>
+        <v>All-Purpose vs Job Compute</v>
       </c>
       <c r="C53" s="3" t="str">
         <f>'Databricks Master Syllabus'!A49</f>
         <v>7. Compute &amp; Cost</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E53" s="3">
         <v>0</v>
@@ -4837,14 +5278,14 @@
       </c>
       <c r="B54" s="2" t="str">
         <f>'Databricks Master Syllabus'!C50</f>
-        <v>Access Modes</v>
+        <v>SQL Warehouses</v>
       </c>
       <c r="C54" s="2" t="str">
         <f>'Databricks Master Syllabus'!A50</f>
         <v>7. Compute &amp; Cost</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E54" s="2">
         <v>0</v>
@@ -4859,14 +5300,14 @@
       </c>
       <c r="B55" s="3" t="str">
         <f>'Databricks Master Syllabus'!C51</f>
-        <v>Compute Policies and Pools</v>
+        <v>Access Modes</v>
       </c>
       <c r="C55" s="3" t="str">
         <f>'Databricks Master Syllabus'!A51</f>
         <v>7. Compute &amp; Cost</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E55" s="3">
         <v>0</v>
@@ -4881,14 +5322,14 @@
       </c>
       <c r="B56" s="2" t="str">
         <f>'Databricks Master Syllabus'!C52</f>
-        <v>DBUs and Cost Levers</v>
+        <v>Photon and Runtime Selection</v>
       </c>
       <c r="C56" s="2" t="str">
         <f>'Databricks Master Syllabus'!A52</f>
         <v>7. Compute &amp; Cost</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E56" s="2">
         <v>0</v>
@@ -4897,20 +5338,20 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
         <v>52</v>
       </c>
       <c r="B57" s="3" t="str">
         <f>'Databricks Master Syllabus'!C53</f>
-        <v>Spark Execution Model</v>
+        <v>Compute Policies, Pools and Autoscaling</v>
       </c>
       <c r="C57" s="3" t="str">
         <f>'Databricks Master Syllabus'!A53</f>
-        <v>8. Spark &amp; Transformation</v>
+        <v>7. Compute &amp; Cost</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E57" s="3">
         <v>0</v>
@@ -4919,20 +5360,20 @@
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
     </row>
-    <row r="58" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>53</v>
       </c>
       <c r="B58" s="2" t="str">
         <f>'Databricks Master Syllabus'!C54</f>
-        <v>DataFrame and SQL Transformations</v>
+        <v>DBUs and Cost Levers</v>
       </c>
       <c r="C58" s="2" t="str">
         <f>'Databricks Master Syllabus'!A54</f>
-        <v>8. Spark &amp; Transformation</v>
+        <v>7. Compute &amp; Cost</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E58" s="2">
         <v>0</v>
@@ -4947,14 +5388,14 @@
       </c>
       <c r="B59" s="3" t="str">
         <f>'Databricks Master Syllabus'!C55</f>
-        <v>Joins, Unions and Deduplication</v>
+        <v>Spark Execution Model</v>
       </c>
       <c r="C59" s="3" t="str">
         <f>'Databricks Master Syllabus'!A55</f>
         <v>8. Spark &amp; Transformation</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E59" s="3">
         <v>0</v>
@@ -4963,20 +5404,20 @@
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>55</v>
       </c>
       <c r="B60" s="2" t="str">
         <f>'Databricks Master Syllabus'!C56</f>
-        <v>Bronze to Silver to Gold</v>
+        <v>DataFrame and SQL Transformations</v>
       </c>
       <c r="C60" s="2" t="str">
         <f>'Databricks Master Syllabus'!A56</f>
         <v>8. Spark &amp; Transformation</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E60" s="2">
         <v>0</v>
@@ -4985,20 +5426,20 @@
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
     </row>
-    <row r="61" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
         <v>56</v>
       </c>
       <c r="B61" s="3" t="str">
         <f>'Databricks Master Syllabus'!C57</f>
-        <v>AQE, Broadcast and Shuffle Partitions</v>
+        <v>Joins, Unions and Deduplication</v>
       </c>
       <c r="C61" s="3" t="str">
         <f>'Databricks Master Syllabus'!A57</f>
         <v>8. Spark &amp; Transformation</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -5013,14 +5454,14 @@
       </c>
       <c r="B62" s="2" t="str">
         <f>'Databricks Master Syllabus'!C58</f>
-        <v>Skew, Salting and Spill</v>
+        <v>Bronze to Silver to Gold</v>
       </c>
       <c r="C62" s="2" t="str">
         <f>'Databricks Master Syllabus'!A58</f>
         <v>8. Spark &amp; Transformation</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E62" s="2">
         <v>0</v>
@@ -5029,20 +5470,20 @@
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A63" s="3">
         <v>58</v>
       </c>
       <c r="B63" s="3" t="str">
         <f>'Databricks Master Syllabus'!C59</f>
-        <v>Disk Cache and the Spark UI</v>
+        <v>AQE, Broadcast and Shuffle Partitions</v>
       </c>
       <c r="C63" s="3" t="str">
         <f>'Databricks Master Syllabus'!A59</f>
         <v>8. Spark &amp; Transformation</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E63" s="3">
         <v>0</v>
@@ -5057,14 +5498,14 @@
       </c>
       <c r="B64" s="2" t="str">
         <f>'Databricks Master Syllabus'!C60</f>
-        <v>Choosing an Ingestion Method</v>
+        <v>Skew, Salting and Spill</v>
       </c>
       <c r="C64" s="2" t="str">
         <f>'Databricks Master Syllabus'!A60</f>
-        <v>9. Ingestion &amp; Streaming</v>
+        <v>8. Spark &amp; Transformation</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E64" s="2">
         <v>0</v>
@@ -5079,14 +5520,14 @@
       </c>
       <c r="B65" s="3" t="str">
         <f>'Databricks Master Syllabus'!C61</f>
-        <v>COPY INTO</v>
+        <v>Disk Cache and the Spark UI</v>
       </c>
       <c r="C65" s="3" t="str">
         <f>'Databricks Master Syllabus'!A61</f>
-        <v>9. Ingestion &amp; Streaming</v>
+        <v>8. Spark &amp; Transformation</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E65" s="3">
         <v>0</v>
@@ -5101,14 +5542,14 @@
       </c>
       <c r="B66" s="2" t="str">
         <f>'Databricks Master Syllabus'!C62</f>
-        <v>Auto Loader File Detection</v>
+        <v>Choosing an Ingestion Method</v>
       </c>
       <c r="C66" s="2" t="str">
         <f>'Databricks Master Syllabus'!A62</f>
         <v>9. Ingestion &amp; Streaming</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E66" s="2">
         <v>0</v>
@@ -5117,20 +5558,20 @@
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
     </row>
-    <row r="67" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="3">
         <v>62</v>
       </c>
       <c r="B67" s="3" t="str">
         <f>'Databricks Master Syllabus'!C63</f>
-        <v>Auto Loader Schema Inference and Evolution</v>
+        <v>COPY INTO</v>
       </c>
       <c r="C67" s="3" t="str">
         <f>'Databricks Master Syllabus'!A63</f>
         <v>9. Ingestion &amp; Streaming</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E67" s="3">
         <v>0</v>
@@ -5145,14 +5586,14 @@
       </c>
       <c r="B68" s="2" t="str">
         <f>'Databricks Master Syllabus'!C64</f>
-        <v>Structured Streaming Checkpoints</v>
+        <v>Auto Loader File Detection</v>
       </c>
       <c r="C68" s="2" t="str">
         <f>'Databricks Master Syllabus'!A64</f>
         <v>9. Ingestion &amp; Streaming</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E68" s="2">
         <v>0</v>
@@ -5167,14 +5608,14 @@
       </c>
       <c r="B69" s="3" t="str">
         <f>'Databricks Master Syllabus'!C65</f>
-        <v>Triggers, Watermarks and Output Modes</v>
+        <v>Auto Loader Schema Inference and Evolution</v>
       </c>
       <c r="C69" s="3" t="str">
         <f>'Databricks Master Syllabus'!A65</f>
         <v>9. Ingestion &amp; Streaming</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E69" s="3">
         <v>0</v>
@@ -5189,14 +5630,14 @@
       </c>
       <c r="B70" s="2" t="str">
         <f>'Databricks Master Syllabus'!C66</f>
-        <v>foreachBatch and Exactly-Once</v>
+        <v>Structured Streaming Checkpoints</v>
       </c>
       <c r="C70" s="2" t="str">
         <f>'Databricks Master Syllabus'!A66</f>
         <v>9. Ingestion &amp; Streaming</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E70" s="2">
         <v>0</v>
@@ -5211,14 +5652,14 @@
       </c>
       <c r="B71" s="3" t="str">
         <f>'Databricks Master Syllabus'!C67</f>
-        <v>Streaming Tables vs Materialized Views</v>
+        <v>Triggers, Watermarks and Output Modes</v>
       </c>
       <c r="C71" s="3" t="str">
         <f>'Databricks Master Syllabus'!A67</f>
-        <v>10. Pipelines &amp; Orchestration</v>
+        <v>9. Ingestion &amp; Streaming</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E71" s="3">
         <v>0</v>
@@ -5233,14 +5674,14 @@
       </c>
       <c r="B72" s="2" t="str">
         <f>'Databricks Master Syllabus'!C68</f>
-        <v>Expectations</v>
+        <v>foreachBatch and Exactly-Once</v>
       </c>
       <c r="C72" s="2" t="str">
         <f>'Databricks Master Syllabus'!A68</f>
-        <v>10. Pipelines &amp; Orchestration</v>
+        <v>9. Ingestion &amp; Streaming</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E72" s="2">
         <v>0</v>
@@ -5255,14 +5696,14 @@
       </c>
       <c r="B73" s="3" t="str">
         <f>'Databricks Master Syllabus'!C69</f>
-        <v>AUTO CDC and SCD Types</v>
+        <v>Recovery, Replay and Backfill</v>
       </c>
       <c r="C73" s="3" t="str">
         <f>'Databricks Master Syllabus'!A69</f>
-        <v>10. Pipelines &amp; Orchestration</v>
+        <v>9. Ingestion &amp; Streaming</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E73" s="3">
         <v>0</v>
@@ -5277,14 +5718,14 @@
       </c>
       <c r="B74" s="2" t="str">
         <f>'Databricks Master Syllabus'!C70</f>
-        <v>Refresh vs Full Refresh</v>
+        <v>Pipeline Datasets and Flows</v>
       </c>
       <c r="C74" s="2" t="str">
         <f>'Databricks Master Syllabus'!A70</f>
         <v>10. Pipelines &amp; Orchestration</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E74" s="2">
         <v>0</v>
@@ -5293,20 +5734,20 @@
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
     </row>
-    <row r="75" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="3">
         <v>70</v>
       </c>
       <c r="B75" s="3" t="str">
         <f>'Databricks Master Syllabus'!C71</f>
-        <v>Lakeflow Jobs: Tasks and Dependencies</v>
+        <v>Expectations</v>
       </c>
       <c r="C75" s="3" t="str">
         <f>'Databricks Master Syllabus'!A71</f>
         <v>10. Pipelines &amp; Orchestration</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E75" s="3">
         <v>0</v>
@@ -5321,14 +5762,14 @@
       </c>
       <c r="B76" s="2" t="str">
         <f>'Databricks Master Syllabus'!C72</f>
-        <v>Run If, Retries and Timeouts</v>
+        <v>AUTO CDC and SCD Types</v>
       </c>
       <c r="C76" s="2" t="str">
         <f>'Databricks Master Syllabus'!A72</f>
         <v>10. Pipelines &amp; Orchestration</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E76" s="2">
         <v>0</v>
@@ -5343,14 +5784,14 @@
       </c>
       <c r="B77" s="3" t="str">
         <f>'Databricks Master Syllabus'!C73</f>
-        <v>Triggers and Repair Runs</v>
+        <v>Refresh vs Full Refresh</v>
       </c>
       <c r="C77" s="3" t="str">
         <f>'Databricks Master Syllabus'!A73</f>
         <v>10. Pipelines &amp; Orchestration</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E77" s="3">
         <v>0</v>
@@ -5359,20 +5800,20 @@
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>73</v>
       </c>
       <c r="B78" s="2" t="str">
         <f>'Databricks Master Syllabus'!C74</f>
-        <v>Databricks with ADF and ADLS</v>
+        <v>Lakeflow Jobs: Tasks and Dependencies</v>
       </c>
       <c r="C78" s="2" t="str">
         <f>'Databricks Master Syllabus'!A74</f>
         <v>10. Pipelines &amp; Orchestration</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E78" s="2">
         <v>0</v>
@@ -5387,14 +5828,14 @@
       </c>
       <c r="B79" s="3" t="str">
         <f>'Databricks Master Syllabus'!C75</f>
-        <v>System Tables and Monitoring</v>
+        <v>Run If, Retries and Timeouts</v>
       </c>
       <c r="C79" s="3" t="str">
         <f>'Databricks Master Syllabus'!A75</f>
-        <v>11. Operate, Deploy &amp; Capstone</v>
+        <v>10. Pipelines &amp; Orchestration</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E79" s="3">
         <v>0</v>
@@ -5403,20 +5844,20 @@
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
     </row>
-    <row r="80" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>75</v>
       </c>
       <c r="B80" s="2" t="str">
         <f>'Databricks Master Syllabus'!C76</f>
-        <v>Pipeline Event Logs and Job Run History</v>
+        <v>Job Concurrency and Limits</v>
       </c>
       <c r="C80" s="2" t="str">
         <f>'Databricks Master Syllabus'!A76</f>
-        <v>11. Operate, Deploy &amp; Capstone</v>
+        <v>10. Pipelines &amp; Orchestration</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E80" s="2">
         <v>0</v>
@@ -5431,14 +5872,14 @@
       </c>
       <c r="B81" s="3" t="str">
         <f>'Databricks Master Syllabus'!C77</f>
-        <v>Identity and Secrets</v>
+        <v>Triggers and Repair Runs</v>
       </c>
       <c r="C81" s="3" t="str">
         <f>'Databricks Master Syllabus'!A77</f>
-        <v>11. Operate, Deploy &amp; Capstone</v>
+        <v>10. Pipelines &amp; Orchestration</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E81" s="3">
         <v>0</v>
@@ -5453,14 +5894,14 @@
       </c>
       <c r="B82" s="2" t="str">
         <f>'Databricks Master Syllabus'!C78</f>
-        <v>Git Folders</v>
+        <v>Databricks with ADF and ADLS</v>
       </c>
       <c r="C82" s="2" t="str">
         <f>'Databricks Master Syllabus'!A78</f>
-        <v>11. Operate, Deploy &amp; Capstone</v>
+        <v>10. Pipelines &amp; Orchestration</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E82" s="2">
         <v>0</v>
@@ -5475,14 +5916,14 @@
       </c>
       <c r="B83" s="3" t="str">
         <f>'Databricks Master Syllabus'!C79</f>
-        <v>Declarative Automation Bundles</v>
+        <v>Three Network Connections</v>
       </c>
       <c r="C83" s="3" t="str">
         <f>'Databricks Master Syllabus'!A79</f>
-        <v>11. Operate, Deploy &amp; Capstone</v>
+        <v>11. Azure Networking for Databricks</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -5491,20 +5932,20 @@
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
     </row>
-    <row r="84" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>79</v>
       </c>
       <c r="B84" s="2" t="str">
         <f>'Databricks Master Syllabus'!C80</f>
-        <v>Capstone: End-to-End Medallion Pipeline</v>
+        <v>Serverless vs Hybrid Workspaces</v>
       </c>
       <c r="C84" s="2" t="str">
         <f>'Databricks Master Syllabus'!A80</f>
-        <v>11. Operate, Deploy &amp; Capstone</v>
+        <v>11. Azure Networking for Databricks</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E84" s="2">
         <v>0</v>
@@ -5512,6 +5953,270 @@
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A85" s="3">
+        <v>80</v>
+      </c>
+      <c r="B85" s="3" t="str">
+        <f>'Databricks Master Syllabus'!C81</f>
+        <v>VNet Injection and Subnet Sizing</v>
+      </c>
+      <c r="C85" s="3" t="str">
+        <f>'Databricks Master Syllabus'!A81</f>
+        <v>11. Azure Networking for Databricks</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="E85" s="3">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A86" s="2">
+        <v>81</v>
+      </c>
+      <c r="B86" s="2" t="str">
+        <f>'Databricks Master Syllabus'!C82</f>
+        <v>Subnet Delegation and NSG Rules</v>
+      </c>
+      <c r="C86" s="2" t="str">
+        <f>'Databricks Master Syllabus'!A82</f>
+        <v>11. Azure Networking for Databricks</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E86" s="2">
+        <v>0</v>
+      </c>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+    </row>
+    <row r="87" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A87" s="3">
+        <v>82</v>
+      </c>
+      <c r="B87" s="3" t="str">
+        <f>'Databricks Master Syllabus'!C83</f>
+        <v>Secure Cluster Connectivity and Egress</v>
+      </c>
+      <c r="C87" s="3" t="str">
+        <f>'Databricks Master Syllabus'!A83</f>
+        <v>11. Azure Networking for Databricks</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="E87" s="3">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A88" s="2">
+        <v>83</v>
+      </c>
+      <c r="B88" s="2" t="str">
+        <f>'Databricks Master Syllabus'!C84</f>
+        <v>Private Link: Three Kinds</v>
+      </c>
+      <c r="C88" s="2" t="str">
+        <f>'Databricks Master Syllabus'!A84</f>
+        <v>11. Azure Networking for Databricks</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E88" s="2">
+        <v>0</v>
+      </c>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+    </row>
+    <row r="89" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A89" s="3">
+        <v>84</v>
+      </c>
+      <c r="B89" s="3" t="str">
+        <f>'Databricks Master Syllabus'!C85</f>
+        <v>Browser Authentication and the Transit VNet</v>
+      </c>
+      <c r="C89" s="3" t="str">
+        <f>'Databricks Master Syllabus'!A85</f>
+        <v>11. Azure Networking for Databricks</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+    </row>
+    <row r="90" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A90" s="2">
+        <v>85</v>
+      </c>
+      <c r="B90" s="2" t="str">
+        <f>'Databricks Master Syllabus'!C86</f>
+        <v>Serverless Connectivity and Storage Firewalls</v>
+      </c>
+      <c r="C90" s="2" t="str">
+        <f>'Databricks Master Syllabus'!A86</f>
+        <v>11. Azure Networking for Databricks</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E90" s="2">
+        <v>0</v>
+      </c>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A91" s="3">
+        <v>86</v>
+      </c>
+      <c r="B91" s="3" t="str">
+        <f>'Databricks Master Syllabus'!C87</f>
+        <v>System Tables and Monitoring</v>
+      </c>
+      <c r="C91" s="3" t="str">
+        <f>'Databricks Master Syllabus'!A87</f>
+        <v>12. Operate, Deploy &amp; Capstone</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+    </row>
+    <row r="92" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A92" s="2">
+        <v>87</v>
+      </c>
+      <c r="B92" s="2" t="str">
+        <f>'Databricks Master Syllabus'!C88</f>
+        <v>Pipeline Event Logs and Job Run History</v>
+      </c>
+      <c r="C92" s="2" t="str">
+        <f>'Databricks Master Syllabus'!A88</f>
+        <v>12. Operate, Deploy &amp; Capstone</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0</v>
+      </c>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A93" s="3">
+        <v>88</v>
+      </c>
+      <c r="B93" s="3" t="str">
+        <f>'Databricks Master Syllabus'!C89</f>
+        <v>Identity and Secrets</v>
+      </c>
+      <c r="C93" s="3" t="str">
+        <f>'Databricks Master Syllabus'!A89</f>
+        <v>12. Operate, Deploy &amp; Capstone</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="E93" s="3">
+        <v>0</v>
+      </c>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A94" s="2">
+        <v>89</v>
+      </c>
+      <c r="B94" s="2" t="str">
+        <f>'Databricks Master Syllabus'!C90</f>
+        <v>Git Folders</v>
+      </c>
+      <c r="C94" s="2" t="str">
+        <f>'Databricks Master Syllabus'!A90</f>
+        <v>12. Operate, Deploy &amp; Capstone</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E94" s="2">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A95" s="3">
+        <v>90</v>
+      </c>
+      <c r="B95" s="3" t="str">
+        <f>'Databricks Master Syllabus'!C91</f>
+        <v>Declarative Automation Bundles</v>
+      </c>
+      <c r="C95" s="3" t="str">
+        <f>'Databricks Master Syllabus'!A91</f>
+        <v>12. Operate, Deploy &amp; Capstone</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="E95" s="3">
+        <v>0</v>
+      </c>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+    </row>
+    <row r="96" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A96" s="2">
+        <v>91</v>
+      </c>
+      <c r="B96" s="2" t="str">
+        <f>'Databricks Master Syllabus'!C92</f>
+        <v>Capstone: End-to-End Medallion Pipeline</v>
+      </c>
+      <c r="C96" s="2" t="str">
+        <f>'Databricks Master Syllabus'!A92</f>
+        <v>12. Operate, Deploy &amp; Capstone</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E96" s="2">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5530,178 +6235,178 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>359</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>317</v>
+        <v>360</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>318</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>319</v>
+        <v>362</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>320</v>
+        <v>363</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>321</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>322</v>
+        <v>365</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>323</v>
+        <v>366</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>324</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>325</v>
+        <v>368</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>326</v>
+        <v>369</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>327</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>329</v>
+        <v>372</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>330</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>331</v>
+        <v>374</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>332</v>
+        <v>375</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>333</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>335</v>
+        <v>378</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>333</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>336</v>
+        <v>379</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>337</v>
+        <v>380</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>333</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>338</v>
+        <v>381</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>339</v>
+        <v>382</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>340</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>341</v>
+        <v>384</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>342</v>
+        <v>385</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>343</v>
+        <v>386</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>344</v>
+        <v>387</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>345</v>
+        <v>388</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>346</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>347</v>
+        <v>390</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>349</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>350</v>
+        <v>393</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>351</v>
+        <v>394</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>349</v>
+        <v>392</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>352</v>
+        <v>395</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>353</v>
+        <v>396</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>354</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>355</v>
+        <v>398</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>333</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>357</v>
+        <v>400</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>358</v>
+        <v>401</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>359</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -5720,130 +6425,130 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>403</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>361</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>362</v>
+        <v>405</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>363</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>364</v>
+        <v>407</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>365</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>366</v>
+        <v>409</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>367</v>
+        <v>410</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>368</v>
+        <v>411</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>369</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>370</v>
+        <v>413</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>371</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>372</v>
+        <v>415</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>373</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>374</v>
+        <v>417</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>375</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>376</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>378</v>
+        <v>421</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>379</v>
+        <v>422</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>380</v>
+        <v>423</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>381</v>
+        <v>424</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>382</v>
+        <v>425</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>383</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>384</v>
+        <v>427</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>385</v>
+        <v>428</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>386</v>
+        <v>429</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>387</v>
+        <v>430</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>388</v>
+        <v>431</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>389</v>
+        <v>432</v>
       </c>
     </row>
   </sheetData>

--- a/docs/research/Databricks_Data_Engineering_Mastery_Roadmap.xlsx
+++ b/docs/research/Databricks_Data_Engineering_Mastery_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\PrepBench\.claude\worktrees\databricks-research-1e243f\docs\research\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34323425-181B-4317-BD98-F283F90A0AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4230A312-1C88-4DD3-BD53-B23662758D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="Journey Progress Tracker" sheetId="2" r:id="rId2"/>
     <sheet name="Databricks Command Reference" sheetId="3" r:id="rId3"/>
     <sheet name="Mental Model" sheetId="4" r:id="rId4"/>
+    <sheet name="Error Catalogue" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="640">
   <si>
     <t>Phase</t>
   </si>
@@ -881,7 +882,7 @@
     <t>Run If, Retries and Timeouts</t>
   </si>
   <si>
-    <t>Master Run if conditions, retry policies (none by default), and timeouts.</t>
+    <t>Master Run if conditions, retry policies (set them explicitly), and timeouts.</t>
   </si>
   <si>
     <t>Configure a cleanup task that runs even when an upstream task fails, and a retry on a flaky task.</t>
@@ -1004,7 +1005,7 @@
     <t>Diagnose a serverless job getting 403 Forbidden from a firewalled ADLS account and give the fix.</t>
   </si>
   <si>
-    <t>12. Operate, Deploy &amp; Capstone</t>
+    <t>12. Operate &amp; Deploy</t>
   </si>
   <si>
     <t>System Tables and Monitoring</t>
@@ -1064,6 +1065,213 @@
     <t>Deploy one job to dev and prod targets with a different schema name per target.</t>
   </si>
   <si>
+    <t>13. Production, Troubleshooting &amp; Capstone</t>
+  </si>
+  <si>
+    <t>Running Streams in Production</t>
+  </si>
+  <si>
+    <t>Master production streaming: jobs compute, Continuous job mode, no autoscaling, automatic restart with backoff, no awaitTermination, one job per critical stream.</t>
+  </si>
+  <si>
+    <t>Review a streaming job's settings and list every change needed before it goes to production.</t>
+  </si>
+  <si>
+    <t>§23.1</t>
+  </si>
+  <si>
+    <t>Stateful Streaming in Production</t>
+  </si>
+  <si>
+    <t>Understand state (aggregations, dropDuplicates, stream joins), RocksDB with changelog checkpointing, and shuffle partitions fixed when the checkpoint is created.</t>
+  </si>
+  <si>
+    <t>Explain why raising spark.sql.shuffle.partitions didn't change a running stateful query, and what would.</t>
+  </si>
+  <si>
+    <t>§23.2</t>
+  </si>
+  <si>
+    <t>Notifications and Alerts</t>
+  </si>
+  <si>
+    <t>Master job and task notifications (failure, duration, streaming backlog), destinations, and Databricks SQL alerts on a query result.</t>
+  </si>
+  <si>
+    <t>Set up notifications so a failing task in a multi-task streaming job is noticed within minutes.</t>
+  </si>
+  <si>
+    <t>§23.3</t>
+  </si>
+  <si>
+    <t>Troubleshooting a Failed Job</t>
+  </si>
+  <si>
+    <t>Master the path from alert to cause: Runs tab, matrix view, task run details, common causes, repair with current settings, continuous-job backoff.</t>
+  </si>
+  <si>
+    <t>Walk through a failed run step by step and decide whether repairing it is safe.</t>
+  </si>
+  <si>
+    <t>§23.4</t>
+  </si>
+  <si>
+    <t>Reading Errors: Conditions and SQLSTATE</t>
+  </si>
+  <si>
+    <t>Understand error conditions, SQLSTATE and message parameters, and why code should match the condition, never the message text.</t>
+  </si>
+  <si>
+    <t>Catch TABLE_OR_VIEW_NOT_FOUND in Python by its condition and print its SQLSTATE in Free Edition.</t>
+  </si>
+  <si>
+    <t>§23.5</t>
+  </si>
+  <si>
+    <t>Write, Schema and MERGE Errors</t>
+  </si>
+  <si>
+    <t>Diagnose column-count mismatches, failed schema merges, incompatible types, duplicate MERGE source rows and append-only tables.</t>
+  </si>
+  <si>
+    <t>Reproduce DELTA_MULTIPLE_SOURCE_ROW_MATCHING_TARGET_ROW_IN_MERGE in Free Edition and fix it.</t>
+  </si>
+  <si>
+    <t>§24.2</t>
+  </si>
+  <si>
+    <t>Concurrent Write Conflicts</t>
+  </si>
+  <si>
+    <t>Diagnose the DELTA_CONCURRENT_* family, metadata and protocol changes, and two streams sharing one checkpoint.</t>
+  </si>
+  <si>
+    <t>Name the likely cause and fix for each of five concurrent-write errors.</t>
+  </si>
+  <si>
+    <t>§24.3, §2.7</t>
+  </si>
+  <si>
+    <t>Streaming Errors</t>
+  </si>
+  <si>
+    <t>Diagnose new-field failures, missing notified files, schema changes under a stream, update/delete commits in a streamed table, and out-of-memory on restart.</t>
+  </si>
+  <si>
+    <t>For each streaming error, say whether a restart, a new checkpoint, an option or more compute is the fix.</t>
+  </si>
+  <si>
+    <t>§24.4, §23.1</t>
+  </si>
+  <si>
+    <t>File, History and Retention Errors</t>
+  </si>
+  <si>
+    <t>Diagnose missing files referenced by the log, VACUUM retention and LITE errors, time travel past retention, and unsupported table features.</t>
+  </si>
+  <si>
+    <t>Explain how a too-short VACUUM retention turned into DELTA_FILE_NOT_FOUND_DETAILED for a stream.</t>
+  </si>
+  <si>
+    <t>§24.5</t>
+  </si>
+  <si>
+    <t>Query Profile and Query History</t>
+  </si>
+  <si>
+    <t>Use query history and the query profile to find the slowest operators, exploding joins and full scans.</t>
+  </si>
+  <si>
+    <t>In Free Edition, open a slow query's profile and name its most expensive operator.</t>
+  </si>
+  <si>
+    <t>§23.6</t>
+  </si>
+  <si>
+    <t>Compute That Won't Start</t>
+  </si>
+  <si>
+    <t>Understand the 'compute plane network is misconfigured' and METASTORE_DOWN symptoms and how to test the network path on Azure.</t>
+  </si>
+  <si>
+    <t>List the endpoints you would test from a VM in the workspace subnet, and why.</t>
+  </si>
+  <si>
+    <t>§23.7, §20</t>
+  </si>
+  <si>
+    <t>Libraries and Init Scripts</t>
+  </si>
+  <si>
+    <t>Understand compute-scoped libraries from volumes, why DBFS libraries are discouraged, and Databricks' advice to avoid init scripts (none on serverless).</t>
+  </si>
+  <si>
+    <t>Move a library install out of an init script into a compute policy and explain the gain.</t>
+  </si>
+  <si>
+    <t>§23.8</t>
+  </si>
+  <si>
+    <t>Runtime Lifecycle and Upgrades</t>
+  </si>
+  <si>
+    <t>Understand the runtime lifecycle (six months of features, LTS fixes for three years, end of support) and feature retirement phases.</t>
+  </si>
+  <si>
+    <t>Plan when a team on an LTS runtime must upgrade and what to test first.</t>
+  </si>
+  <si>
+    <t>§23.9</t>
+  </si>
+  <si>
+    <t>Environment Isolation and Catalog Strategy</t>
+  </si>
+  <si>
+    <t>Understand separate workspaces for environments or business units, their costs, and catalogs as data domains with separate storage.</t>
+  </si>
+  <si>
+    <t>Propose a dev/test/prod layout of workspaces and catalogs and name one trade-off.</t>
+  </si>
+  <si>
+    <t>§23.10</t>
+  </si>
+  <si>
+    <t>Encryption and Customer-Managed Keys</t>
+  </si>
+  <si>
+    <t>Understand Azure customer-managed keys for managed disks, managed services and the DBFS root, and that traffic between workers isn't encrypted by default.</t>
+  </si>
+  <si>
+    <t>Say which key protects notebook source, cluster temp disks and the workspace storage account.</t>
+  </si>
+  <si>
+    <t>§23.11</t>
+  </si>
+  <si>
+    <t>High Availability and Disaster Recovery</t>
+  </si>
+  <si>
+    <t>Understand zone-level HA vs cross-region DR, RPO and RTO, active-passive, managed DR, Deep Clone replication, and why DR doesn't fix corruption.</t>
+  </si>
+  <si>
+    <t>Explain to a sponsor why a DR region didn't help when a bad job corrupted a table, and what would have.</t>
+  </si>
+  <si>
+    <t>§23.12</t>
+  </si>
+  <si>
+    <t>Testing Databricks Code</t>
+  </si>
+  <si>
+    <t>Understand unit testing functions with pytest and SQL UDFs, kept outside notebooks in a Git folder.</t>
+  </si>
+  <si>
+    <t>Write one pytest test for a transformation function and run it from a Git folder.</t>
+  </si>
+  <si>
+    <t>§23.13</t>
+  </si>
+  <si>
     <t>Capstone: End-to-End Medallion Pipeline</t>
   </si>
   <si>
@@ -1073,7 +1281,7 @@
     <t>Run the pipeline in Free Edition, grant a reader group on gold, and explain every design choice to a reviewer.</t>
   </si>
   <si>
-    <t>1-23</t>
+    <t>1-24</t>
   </si>
   <si>
     <t>all</t>
@@ -1335,6 +1543,420 @@
   </si>
   <si>
     <t>Ore, refined metal, finished jewellery: each stage is cleaner and closer to what the customer wants.</t>
+  </si>
+  <si>
+    <t>Error Condition (SQLSTATE)</t>
+  </si>
+  <si>
+    <t>What You See</t>
+  </si>
+  <si>
+    <t>Likely Cause and Fix</t>
+  </si>
+  <si>
+    <t>Taught In (#)</t>
+  </si>
+  <si>
+    <t>TABLE_OR_VIEW_NOT_FOUND (42P01)</t>
+  </si>
+  <si>
+    <t>The table or view can't be found</t>
+  </si>
+  <si>
+    <t>Wrong name, wrong current schema, or no USE CATALOG/USE SCHEMA. Fix: Qualify catalog.schema.table; check grants.</t>
+  </si>
+  <si>
+    <t>38, 95</t>
+  </si>
+  <si>
+    <t>SCHEMA_NOT_FOUND (42704)</t>
+  </si>
+  <si>
+    <t>The schema can't be found</t>
+  </si>
+  <si>
+    <t>Wrong name or catalog. Fix: Qualify the name with its catalog.</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>UNRESOLVED_COLUMN (42703)</t>
+  </si>
+  <si>
+    <t>A column or parameter can't be resolved</t>
+  </si>
+  <si>
+    <t>Misspelt or missing column. Fix: Check the DataFrame's columns.</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>INSUFFICIENT_PERMISSIONS (42501)</t>
+  </si>
+  <si>
+    <t>Insufficient privileges</t>
+  </si>
+  <si>
+    <t>A missing privilege in the USE CATALOG + USE SCHEMA + object chain. Fix: Grant the missing privilege.</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>INSUFFICIENT_PERMISSIONS_EXT_LOC (42501)</t>
+  </si>
+  <si>
+    <t>Insufficient privileges on an external location</t>
+  </si>
+  <si>
+    <t>No privilege on the external location. Fix: Grant it on the external location.</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>CAST_INVALID_INPUT (22018)</t>
+  </si>
+  <si>
+    <t>A malformed value can't be cast</t>
+  </si>
+  <si>
+    <t>Bad source data. Fix: Fix the data or type; try_cast returns NULL.</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>DIVIDE_BY_ZERO (22012)</t>
+  </si>
+  <si>
+    <t>Division by zero</t>
+  </si>
+  <si>
+    <t>A zero divisor. Fix: try_divide returns NULL.</t>
+  </si>
+  <si>
+    <t>DELTA_INSERT_COLUMN_ARITY_MISMATCH (42802)</t>
+  </si>
+  <si>
+    <t>Target has N columns, the data has M</t>
+  </si>
+  <si>
+    <t>Source and table schemas differ. Fix: Align columns or evolve the schema on purpose.</t>
+  </si>
+  <si>
+    <t>27, 96</t>
+  </si>
+  <si>
+    <t>DELTA_FAILED_TO_MERGE_FIELDS (22005)</t>
+  </si>
+  <si>
+    <t>Two field definitions can't be merged</t>
+  </si>
+  <si>
+    <t>Type conflict during schema merge. Fix: Cast the source or change the table.</t>
+  </si>
+  <si>
+    <t>28, 96</t>
+  </si>
+  <si>
+    <t>DELTA_MERGE_INCOMPATIBLE_DATATYPE (42K09)</t>
+  </si>
+  <si>
+    <t>Incompatible data types can't be merged</t>
+  </si>
+  <si>
+    <t>Type conflict. Fix: Cast the source or change the table.</t>
+  </si>
+  <si>
+    <t>DELTA_MULTIPLE_SOURCE_ROW_MATCHING_TARGET_ROW_IN_MERGE (21506)</t>
+  </si>
+  <si>
+    <t>Several source rows match one target row</t>
+  </si>
+  <si>
+    <t>Duplicate keys in the MERGE source. Fix: Deduplicate the source first.</t>
+  </si>
+  <si>
+    <t>29, 96</t>
+  </si>
+  <si>
+    <t>DELTA_CANNOT_MODIFY_APPEND_ONLY (42809)</t>
+  </si>
+  <si>
+    <t>The table only allows appends</t>
+  </si>
+  <si>
+    <t>Table property set to append-only. Fix: Change it only if updates are really allowed.</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>DELTA_CONCURRENT_APPEND (2D521)</t>
+  </si>
+  <si>
+    <t>A concurrent operation added conflicting data</t>
+  </si>
+  <si>
+    <t>Two writers overlapping. Fix: Retry; reduce overlap.</t>
+  </si>
+  <si>
+    <t>18, 97</t>
+  </si>
+  <si>
+    <t>DELTA_CONCURRENT_DELETE_READ (2D521)</t>
+  </si>
+  <si>
+    <t>Data this transaction read was deleted concurrently</t>
+  </si>
+  <si>
+    <t>An overlapping delete. Fix: Retry.</t>
+  </si>
+  <si>
+    <t>DELTA_CONCURRENT_WRITE (2D521)</t>
+  </si>
+  <si>
+    <t>New data was written since this transaction read</t>
+  </si>
+  <si>
+    <t>A concurrent write. Fix: Try the operation again.</t>
+  </si>
+  <si>
+    <t>DELTA_CONCURRENT_TRANSACTION (2D521)</t>
+  </si>
+  <si>
+    <t>Several streams use the same checkpoint</t>
+  </si>
+  <si>
+    <t>A duplicate run of one streaming query. Fix: One checkpoint per query; stop the duplicate.</t>
+  </si>
+  <si>
+    <t>65, 97</t>
+  </si>
+  <si>
+    <t>DELTA_METADATA_CHANGED (2D521)</t>
+  </si>
+  <si>
+    <t>Metadata changed by a concurrent update</t>
+  </si>
+  <si>
+    <t>A schema or property change during writes. Fix: Retry; schedule changes away from writes.</t>
+  </si>
+  <si>
+    <t>19, 97</t>
+  </si>
+  <si>
+    <t>DELTA_PROTOCOL_CHANGED (2D521)</t>
+  </si>
+  <si>
+    <t>Protocol changed by a concurrent update</t>
+  </si>
+  <si>
+    <t>A feature enabled during writes. Fix: Retry.</t>
+  </si>
+  <si>
+    <t>20, 97</t>
+  </si>
+  <si>
+    <t>UNKNOWN_FIELD_EXCEPTION (KD003)</t>
+  </si>
+  <si>
+    <t>New fields found while parsing</t>
+  </si>
+  <si>
+    <t>Auto Loader addNewColumns met a new column. Fix: Let the job restart; it resumes with the new schema.</t>
+  </si>
+  <si>
+    <t>64, 98</t>
+  </si>
+  <si>
+    <t>CLOUD_FILE_SOURCE_FILE_NOT_FOUND (42K03)</t>
+  </si>
+  <si>
+    <t>A notified file no longer exists</t>
+  </si>
+  <si>
+    <t>File deleted before it was processed. Fix: Don't delete files before they are processed.</t>
+  </si>
+  <si>
+    <t>63, 98</t>
+  </si>
+  <si>
+    <t>DELTA_SCHEMA_CHANGED (KD007)</t>
+  </si>
+  <si>
+    <t>The source schema changed under the stream</t>
+  </si>
+  <si>
+    <t>A schema change on a streamed table. Fix: Restart; if it repeats, use a new checkpoint.</t>
+  </si>
+  <si>
+    <t>65, 98</t>
+  </si>
+  <si>
+    <t>DELTA_STREAMING_INCOMPATIBLE_SCHEMA_CHANGE (42KD4)</t>
+  </si>
+  <si>
+    <t>Rename, drop or type change on a streamed table</t>
+  </si>
+  <si>
+    <t>A read-incompatible schema change. Fix: Follow the linked doc, or use a schema tracking location.</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>DELTA_SOURCE_TABLE_IGNORE_CHANGES (0A000)</t>
+  </si>
+  <si>
+    <t>An update or delete in a table read as a stream</t>
+  </si>
+  <si>
+    <t>Streams expect append-only sources. Fix: skipChangeCommits, or a fresh checkpoint / full refresh.</t>
+  </si>
+  <si>
+    <t>68, 98</t>
+  </si>
+  <si>
+    <t>DELTA_FILE_NOT_FOUND_DETAILED (42K03)</t>
+  </si>
+  <si>
+    <t>A file referenced in the log is missing</t>
+  </si>
+  <si>
+    <t>Manual deletion, or VACUUM with too short a retention. Fix: Never delete table files directly; restart with a new checkpoint.</t>
+  </si>
+  <si>
+    <t>25, 99</t>
+  </si>
+  <si>
+    <t>DELTA_VACUUM_RETENTION_PERIOD_TOO_SHORT (22003)</t>
+  </si>
+  <si>
+    <t>Retention below the safety threshold</t>
+  </si>
+  <si>
+    <t>VACUUM with a short retention. Fix: Keep at least 7 days.</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>DELTA_CANNOT_VACUUM_LITE (55000)</t>
+  </si>
+  <si>
+    <t>LITE can't find all files from the log</t>
+  </si>
+  <si>
+    <t>Untracked files in the directory. Fix: Run VACUUM FULL.</t>
+  </si>
+  <si>
+    <t>DELTA_TIMESTAMP_EARLIER_THAN_COMMIT_RETENTION (42816)</t>
+  </si>
+  <si>
+    <t>Timestamp older than the earliest kept version</t>
+  </si>
+  <si>
+    <t>History past log retention. Fix: Use a later timestamp; raise retention in advance.</t>
+  </si>
+  <si>
+    <t>24, 99</t>
+  </si>
+  <si>
+    <t>DELTA_CANNOT_RESTORE_TABLE_VERSION (22003)</t>
+  </si>
+  <si>
+    <t>Version outside the available range</t>
+  </si>
+  <si>
+    <t>Version expired or never existed. Fix: Choose a version in range.</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>DELTA_UNSUPPORTED_FEATURES_FOR_READ (56038)</t>
+  </si>
+  <si>
+    <t>Table needs reader features this runtime lacks</t>
+  </si>
+  <si>
+    <t>Feature enabled by a newer writer. Fix: Use a newer runtime or client.</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>FAILED_READ_FILE (KD001)</t>
+  </si>
+  <si>
+    <t>Error reading a file</t>
+  </si>
+  <si>
+    <t>A corrupt or unexpected file. Fix: Read the condition's details.</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>Event: compute plane network is misconfigured</t>
+  </si>
+  <si>
+    <t>Node daemon ping timeout; cluster terminated</t>
+  </si>
+  <si>
+    <t>Routing or firewall blocks the control plane. Fix: Test the path from a VM in the workspace subnet.</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>Event: METASTORE_DOWN</t>
+  </si>
+  <si>
+    <t>The metastore is unreachable from compute</t>
+  </si>
+  <si>
+    <t>A web application firewall or proxy in the path. Fix: Take the proxy out of the path.</t>
+  </si>
+  <si>
+    <t>HTTP 403 Forbidden (serverless to storage)</t>
+  </si>
+  <si>
+    <t>Serverless can't read a firewalled storage account</t>
+  </si>
+  <si>
+    <t>Allow-listed serverless subnet IDs no longer work. Fix: Network security perimeter plus the AzureDatabricksServerless tag.</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>HTTP 429 Too Many Requests (jobs)</t>
+  </si>
+  <si>
+    <t>Too many concurrent task runs</t>
+  </si>
+  <si>
+    <t>Over 2,000 concurrent task runs in a workspace. Fix: Spread or reduce concurrent runs.</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>Out of memory after a stream restart</t>
+  </si>
+  <si>
+    <t>The replanned micro-batch fails again</t>
+  </si>
+  <si>
+    <t>The batch planned before the failure is too large. Fix: Scale up the compute to get past it.</t>
+  </si>
+  <si>
+    <t>91, 98</t>
   </si>
 </sst>
 </file>
@@ -1715,7 +2337,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -4092,39 +4714,481 @@
         <v>338</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="B92" s="2">
         <v>91</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F92" s="2">
-        <v>10</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>345</v>
+        <v>3</v>
+      </c>
+      <c r="G92" s="2">
+        <v>24</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C93" s="4" t="s">
+    <row r="93" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A93" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B93" s="3">
+        <v>92</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="F93" s="4">
-        <f>SUM(F2:F92)</f>
-        <v>217</v>
+      <c r="D93" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F93" s="3">
+        <v>2</v>
+      </c>
+      <c r="G93" s="3">
+        <v>24</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A94" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B94" s="2">
+        <v>93</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F94" s="2">
+        <v>2</v>
+      </c>
+      <c r="G94" s="2">
+        <v>24</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A95" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B95" s="3">
+        <v>94</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F95" s="3">
+        <v>3</v>
+      </c>
+      <c r="G95" s="3">
+        <v>24</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A96" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B96" s="2">
+        <v>95</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F96" s="2">
+        <v>2</v>
+      </c>
+      <c r="G96" s="2">
+        <v>24</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A97" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B97" s="3">
+        <v>96</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="F97" s="3">
+        <v>2</v>
+      </c>
+      <c r="G97" s="3">
+        <v>24</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A98" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B98" s="2">
+        <v>97</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F98" s="2">
+        <v>2</v>
+      </c>
+      <c r="G98" s="2">
+        <v>24</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A99" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B99" s="3">
+        <v>98</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="F99" s="3">
+        <v>3</v>
+      </c>
+      <c r="G99" s="3">
+        <v>24</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A100" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B100" s="2">
+        <v>99</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F100" s="2">
+        <v>2</v>
+      </c>
+      <c r="G100" s="2">
+        <v>24</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A101" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B101" s="3">
+        <v>100</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="F101" s="3">
+        <v>2</v>
+      </c>
+      <c r="G101" s="3">
+        <v>24</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A102" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B102" s="2">
+        <v>101</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F102" s="2">
+        <v>2</v>
+      </c>
+      <c r="G102" s="2">
+        <v>24</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A103" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B103" s="3">
+        <v>102</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="F103" s="3">
+        <v>2</v>
+      </c>
+      <c r="G103" s="3">
+        <v>24</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A104" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B104" s="2">
+        <v>103</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="F104" s="2">
+        <v>1</v>
+      </c>
+      <c r="G104" s="2">
+        <v>24</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A105" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B105" s="3">
+        <v>104</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="F105" s="3">
+        <v>2</v>
+      </c>
+      <c r="G105" s="3">
+        <v>24</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A106" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B106" s="2">
+        <v>105</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F106" s="2">
+        <v>2</v>
+      </c>
+      <c r="G106" s="2">
+        <v>24</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+      <c r="A107" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B107" s="3">
+        <v>106</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F107" s="3">
+        <v>3</v>
+      </c>
+      <c r="G107" s="3">
+        <v>24</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A108" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B108" s="2">
+        <v>107</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F108" s="2">
+        <v>2</v>
+      </c>
+      <c r="G108" s="2">
+        <v>24</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A109" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B109" s="3">
+        <v>108</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="F109" s="3">
+        <v>10</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C110" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="F110" s="4">
+        <f>SUM(F2:F109)</f>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -4134,7 +5198,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4148,45 +5212,45 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>348</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="28" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>349</v>
+        <v>418</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>350</v>
+        <v>419</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>351</v>
+        <v>420</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>353</v>
+        <v>422</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
-        <f>COUNTA(B6:B96)</f>
-        <v>91</v>
+        <f>COUNTA(B6:B113)</f>
+        <v>108</v>
       </c>
       <c r="B3" s="5">
-        <f>COUNTIF(D6:D96,"Completed")</f>
+        <f>COUNTIF(D6:D113,"Completed")</f>
         <v>0</v>
       </c>
       <c r="C3" s="5">
-        <f>COUNTIF(D6:D96,"In Progress")</f>
+        <f>COUNTIF(D6:D113,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="D3" s="5">
-        <f>COUNTIF(D6:D96,"Not Started")</f>
-        <v>91</v>
+        <f>COUNTIF(D6:D113,"Not Started")</f>
+        <v>108</v>
       </c>
       <c r="E3" s="6">
-        <f>AVERAGE(E6:E96)/100</f>
+        <f>AVERAGE(E6:E113)/100</f>
         <v>0</v>
       </c>
     </row>
@@ -4201,19 +5265,19 @@
         <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>354</v>
+        <v>423</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>355</v>
+        <v>424</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>356</v>
+        <v>425</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>357</v>
+        <v>426</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>358</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -4229,7 +5293,7 @@
         <v>1. Lakehouse &amp; Platform Foundations</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
@@ -4251,7 +5315,7 @@
         <v>1. Lakehouse &amp; Platform Foundations</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
@@ -4273,7 +5337,7 @@
         <v>1. Lakehouse &amp; Platform Foundations</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
@@ -4295,7 +5359,7 @@
         <v>1. Lakehouse &amp; Platform Foundations</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
@@ -4317,7 +5381,7 @@
         <v>1. Lakehouse &amp; Platform Foundations</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E10" s="2">
         <v>0</v>
@@ -4339,7 +5403,7 @@
         <v>1. Lakehouse &amp; Platform Foundations</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E11" s="3">
         <v>0</v>
@@ -4361,7 +5425,7 @@
         <v>2. Parquet: The File Format</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E12" s="2">
         <v>0</v>
@@ -4383,7 +5447,7 @@
         <v>2. Parquet: The File Format</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E13" s="3">
         <v>0</v>
@@ -4405,7 +5469,7 @@
         <v>2. Parquet: The File Format</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -4427,7 +5491,7 @@
         <v>2. Parquet: The File Format</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -4449,7 +5513,7 @@
         <v>2. Parquet: The File Format</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
@@ -4471,7 +5535,7 @@
         <v>2. Parquet: The File Format</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
@@ -4493,7 +5557,7 @@
         <v>3. Delta Lake Internals</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E18" s="2">
         <v>0</v>
@@ -4515,7 +5579,7 @@
         <v>3. Delta Lake Internals</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E19" s="3">
         <v>0</v>
@@ -4537,7 +5601,7 @@
         <v>3. Delta Lake Internals</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E20" s="2">
         <v>0</v>
@@ -4559,7 +5623,7 @@
         <v>3. Delta Lake Internals</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E21" s="3">
         <v>0</v>
@@ -4581,7 +5645,7 @@
         <v>3. Delta Lake Internals</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
@@ -4603,7 +5667,7 @@
         <v>3. Delta Lake Internals</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
@@ -4625,7 +5689,7 @@
         <v>3. Delta Lake Internals</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E24" s="2">
         <v>0</v>
@@ -4647,7 +5711,7 @@
         <v>3. Delta Lake Internals</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E25" s="3">
         <v>0</v>
@@ -4669,7 +5733,7 @@
         <v>3. Delta Lake Internals</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E26" s="2">
         <v>0</v>
@@ -4691,7 +5755,7 @@
         <v>4. Delta Lake Operations</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E27" s="3">
         <v>0</v>
@@ -4713,7 +5777,7 @@
         <v>4. Delta Lake Operations</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E28" s="2">
         <v>0</v>
@@ -4735,7 +5799,7 @@
         <v>4. Delta Lake Operations</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -4757,7 +5821,7 @@
         <v>4. Delta Lake Operations</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E30" s="2">
         <v>0</v>
@@ -4779,7 +5843,7 @@
         <v>4. Delta Lake Operations</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E31" s="3">
         <v>0</v>
@@ -4801,7 +5865,7 @@
         <v>4. Delta Lake Operations</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E32" s="2">
         <v>0</v>
@@ -4823,7 +5887,7 @@
         <v>4. Delta Lake Operations</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E33" s="3">
         <v>0</v>
@@ -4845,7 +5909,7 @@
         <v>4. Delta Lake Operations</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E34" s="2">
         <v>0</v>
@@ -4867,7 +5931,7 @@
         <v>4. Delta Lake Operations</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E35" s="3">
         <v>0</v>
@@ -4889,7 +5953,7 @@
         <v>5. Data Layout &amp; Table Optimization</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E36" s="2">
         <v>0</v>
@@ -4911,7 +5975,7 @@
         <v>5. Data Layout &amp; Table Optimization</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E37" s="3">
         <v>0</v>
@@ -4933,7 +5997,7 @@
         <v>5. Data Layout &amp; Table Optimization</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E38" s="2">
         <v>0</v>
@@ -4955,7 +6019,7 @@
         <v>5. Data Layout &amp; Table Optimization</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E39" s="3">
         <v>0</v>
@@ -4977,7 +6041,7 @@
         <v>5. Data Layout &amp; Table Optimization</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E40" s="2">
         <v>0</v>
@@ -4999,7 +6063,7 @@
         <v>5. Data Layout &amp; Table Optimization</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E41" s="3">
         <v>0</v>
@@ -5021,7 +6085,7 @@
         <v>5. Data Layout &amp; Table Optimization</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E42" s="2">
         <v>0</v>
@@ -5043,7 +6107,7 @@
         <v>6. Unity Catalog &amp; Governance</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
@@ -5065,7 +6129,7 @@
         <v>6. Unity Catalog &amp; Governance</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E44" s="2">
         <v>0</v>
@@ -5087,7 +6151,7 @@
         <v>6. Unity Catalog &amp; Governance</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
@@ -5109,7 +6173,7 @@
         <v>6. Unity Catalog &amp; Governance</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E46" s="2">
         <v>0</v>
@@ -5131,7 +6195,7 @@
         <v>6. Unity Catalog &amp; Governance</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E47" s="3">
         <v>0</v>
@@ -5153,7 +6217,7 @@
         <v>6. Unity Catalog &amp; Governance</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E48" s="2">
         <v>0</v>
@@ -5175,7 +6239,7 @@
         <v>6. Unity Catalog &amp; Governance</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -5197,7 +6261,7 @@
         <v>6. Unity Catalog &amp; Governance</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E50" s="2">
         <v>0</v>
@@ -5219,7 +6283,7 @@
         <v>6. Unity Catalog &amp; Governance</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E51" s="3">
         <v>0</v>
@@ -5241,7 +6305,7 @@
         <v>7. Compute &amp; Cost</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E52" s="2">
         <v>0</v>
@@ -5263,7 +6327,7 @@
         <v>7. Compute &amp; Cost</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E53" s="3">
         <v>0</v>
@@ -5285,7 +6349,7 @@
         <v>7. Compute &amp; Cost</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E54" s="2">
         <v>0</v>
@@ -5307,7 +6371,7 @@
         <v>7. Compute &amp; Cost</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E55" s="3">
         <v>0</v>
@@ -5329,7 +6393,7 @@
         <v>7. Compute &amp; Cost</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E56" s="2">
         <v>0</v>
@@ -5351,7 +6415,7 @@
         <v>7. Compute &amp; Cost</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E57" s="3">
         <v>0</v>
@@ -5373,7 +6437,7 @@
         <v>7. Compute &amp; Cost</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E58" s="2">
         <v>0</v>
@@ -5395,7 +6459,7 @@
         <v>8. Spark &amp; Transformation</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E59" s="3">
         <v>0</v>
@@ -5417,7 +6481,7 @@
         <v>8. Spark &amp; Transformation</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E60" s="2">
         <v>0</v>
@@ -5439,7 +6503,7 @@
         <v>8. Spark &amp; Transformation</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -5461,7 +6525,7 @@
         <v>8. Spark &amp; Transformation</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E62" s="2">
         <v>0</v>
@@ -5483,7 +6547,7 @@
         <v>8. Spark &amp; Transformation</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E63" s="3">
         <v>0</v>
@@ -5505,7 +6569,7 @@
         <v>8. Spark &amp; Transformation</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E64" s="2">
         <v>0</v>
@@ -5527,7 +6591,7 @@
         <v>8. Spark &amp; Transformation</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E65" s="3">
         <v>0</v>
@@ -5549,7 +6613,7 @@
         <v>9. Ingestion &amp; Streaming</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E66" s="2">
         <v>0</v>
@@ -5571,7 +6635,7 @@
         <v>9. Ingestion &amp; Streaming</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E67" s="3">
         <v>0</v>
@@ -5593,7 +6657,7 @@
         <v>9. Ingestion &amp; Streaming</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E68" s="2">
         <v>0</v>
@@ -5615,7 +6679,7 @@
         <v>9. Ingestion &amp; Streaming</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E69" s="3">
         <v>0</v>
@@ -5637,7 +6701,7 @@
         <v>9. Ingestion &amp; Streaming</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E70" s="2">
         <v>0</v>
@@ -5659,7 +6723,7 @@
         <v>9. Ingestion &amp; Streaming</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E71" s="3">
         <v>0</v>
@@ -5681,7 +6745,7 @@
         <v>9. Ingestion &amp; Streaming</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E72" s="2">
         <v>0</v>
@@ -5703,7 +6767,7 @@
         <v>9. Ingestion &amp; Streaming</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E73" s="3">
         <v>0</v>
@@ -5725,7 +6789,7 @@
         <v>10. Pipelines &amp; Orchestration</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E74" s="2">
         <v>0</v>
@@ -5747,7 +6811,7 @@
         <v>10. Pipelines &amp; Orchestration</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E75" s="3">
         <v>0</v>
@@ -5769,7 +6833,7 @@
         <v>10. Pipelines &amp; Orchestration</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E76" s="2">
         <v>0</v>
@@ -5791,7 +6855,7 @@
         <v>10. Pipelines &amp; Orchestration</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E77" s="3">
         <v>0</v>
@@ -5813,7 +6877,7 @@
         <v>10. Pipelines &amp; Orchestration</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E78" s="2">
         <v>0</v>
@@ -5835,7 +6899,7 @@
         <v>10. Pipelines &amp; Orchestration</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E79" s="3">
         <v>0</v>
@@ -5857,7 +6921,7 @@
         <v>10. Pipelines &amp; Orchestration</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E80" s="2">
         <v>0</v>
@@ -5879,7 +6943,7 @@
         <v>10. Pipelines &amp; Orchestration</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E81" s="3">
         <v>0</v>
@@ -5901,7 +6965,7 @@
         <v>10. Pipelines &amp; Orchestration</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E82" s="2">
         <v>0</v>
@@ -5923,7 +6987,7 @@
         <v>11. Azure Networking for Databricks</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -5945,7 +7009,7 @@
         <v>11. Azure Networking for Databricks</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E84" s="2">
         <v>0</v>
@@ -5967,7 +7031,7 @@
         <v>11. Azure Networking for Databricks</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E85" s="3">
         <v>0</v>
@@ -5989,7 +7053,7 @@
         <v>11. Azure Networking for Databricks</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E86" s="2">
         <v>0</v>
@@ -6011,7 +7075,7 @@
         <v>11. Azure Networking for Databricks</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E87" s="3">
         <v>0</v>
@@ -6033,7 +7097,7 @@
         <v>11. Azure Networking for Databricks</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E88" s="2">
         <v>0</v>
@@ -6055,7 +7119,7 @@
         <v>11. Azure Networking for Databricks</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E89" s="3">
         <v>0</v>
@@ -6077,7 +7141,7 @@
         <v>11. Azure Networking for Databricks</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E90" s="2">
         <v>0</v>
@@ -6096,10 +7160,10 @@
       </c>
       <c r="C91" s="3" t="str">
         <f>'Databricks Master Syllabus'!A87</f>
-        <v>12. Operate, Deploy &amp; Capstone</v>
+        <v>12. Operate &amp; Deploy</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -6118,10 +7182,10 @@
       </c>
       <c r="C92" s="2" t="str">
         <f>'Databricks Master Syllabus'!A88</f>
-        <v>12. Operate, Deploy &amp; Capstone</v>
+        <v>12. Operate &amp; Deploy</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E92" s="2">
         <v>0</v>
@@ -6140,10 +7204,10 @@
       </c>
       <c r="C93" s="3" t="str">
         <f>'Databricks Master Syllabus'!A89</f>
-        <v>12. Operate, Deploy &amp; Capstone</v>
+        <v>12. Operate &amp; Deploy</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E93" s="3">
         <v>0</v>
@@ -6162,10 +7226,10 @@
       </c>
       <c r="C94" s="2" t="str">
         <f>'Databricks Master Syllabus'!A90</f>
-        <v>12. Operate, Deploy &amp; Capstone</v>
+        <v>12. Operate &amp; Deploy</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E94" s="2">
         <v>0</v>
@@ -6184,10 +7248,10 @@
       </c>
       <c r="C95" s="3" t="str">
         <f>'Databricks Master Syllabus'!A91</f>
-        <v>12. Operate, Deploy &amp; Capstone</v>
+        <v>12. Operate &amp; Deploy</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E95" s="3">
         <v>0</v>
@@ -6202,14 +7266,14 @@
       </c>
       <c r="B96" s="2" t="str">
         <f>'Databricks Master Syllabus'!C92</f>
-        <v>Capstone: End-to-End Medallion Pipeline</v>
+        <v>Running Streams in Production</v>
       </c>
       <c r="C96" s="2" t="str">
         <f>'Databricks Master Syllabus'!A92</f>
-        <v>12. Operate, Deploy &amp; Capstone</v>
+        <v>13. Production, Troubleshooting &amp; Capstone</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="E96" s="2">
         <v>0</v>
@@ -6217,6 +7281,380 @@
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
+    </row>
+    <row r="97" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A97" s="3">
+        <v>92</v>
+      </c>
+      <c r="B97" s="3" t="str">
+        <f>'Databricks Master Syllabus'!C93</f>
+        <v>Stateful Streaming in Production</v>
+      </c>
+      <c r="C97" s="3" t="str">
+        <f>'Databricks Master Syllabus'!A93</f>
+        <v>13. Production, Troubleshooting &amp; Capstone</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E97" s="3">
+        <v>0</v>
+      </c>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+    </row>
+    <row r="98" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A98" s="2">
+        <v>93</v>
+      </c>
+      <c r="B98" s="2" t="str">
+        <f>'Databricks Master Syllabus'!C94</f>
+        <v>Notifications and Alerts</v>
+      </c>
+      <c r="C98" s="2" t="str">
+        <f>'Databricks Master Syllabus'!A94</f>
+        <v>13. Production, Troubleshooting &amp; Capstone</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E98" s="2">
+        <v>0</v>
+      </c>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+    </row>
+    <row r="99" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A99" s="3">
+        <v>94</v>
+      </c>
+      <c r="B99" s="3" t="str">
+        <f>'Databricks Master Syllabus'!C95</f>
+        <v>Troubleshooting a Failed Job</v>
+      </c>
+      <c r="C99" s="3" t="str">
+        <f>'Databricks Master Syllabus'!A95</f>
+        <v>13. Production, Troubleshooting &amp; Capstone</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E99" s="3">
+        <v>0</v>
+      </c>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+    </row>
+    <row r="100" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A100" s="2">
+        <v>95</v>
+      </c>
+      <c r="B100" s="2" t="str">
+        <f>'Databricks Master Syllabus'!C96</f>
+        <v>Reading Errors: Conditions and SQLSTATE</v>
+      </c>
+      <c r="C100" s="2" t="str">
+        <f>'Databricks Master Syllabus'!A96</f>
+        <v>13. Production, Troubleshooting &amp; Capstone</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E100" s="2">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+    </row>
+    <row r="101" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A101" s="3">
+        <v>96</v>
+      </c>
+      <c r="B101" s="3" t="str">
+        <f>'Databricks Master Syllabus'!C97</f>
+        <v>Write, Schema and MERGE Errors</v>
+      </c>
+      <c r="C101" s="3" t="str">
+        <f>'Databricks Master Syllabus'!A97</f>
+        <v>13. Production, Troubleshooting &amp; Capstone</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+    </row>
+    <row r="102" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A102" s="2">
+        <v>97</v>
+      </c>
+      <c r="B102" s="2" t="str">
+        <f>'Databricks Master Syllabus'!C98</f>
+        <v>Concurrent Write Conflicts</v>
+      </c>
+      <c r="C102" s="2" t="str">
+        <f>'Databricks Master Syllabus'!A98</f>
+        <v>13. Production, Troubleshooting &amp; Capstone</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E102" s="2">
+        <v>0</v>
+      </c>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+    </row>
+    <row r="103" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A103" s="3">
+        <v>98</v>
+      </c>
+      <c r="B103" s="3" t="str">
+        <f>'Databricks Master Syllabus'!C99</f>
+        <v>Streaming Errors</v>
+      </c>
+      <c r="C103" s="3" t="str">
+        <f>'Databricks Master Syllabus'!A99</f>
+        <v>13. Production, Troubleshooting &amp; Capstone</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E103" s="3">
+        <v>0</v>
+      </c>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+    </row>
+    <row r="104" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A104" s="2">
+        <v>99</v>
+      </c>
+      <c r="B104" s="2" t="str">
+        <f>'Databricks Master Syllabus'!C100</f>
+        <v>File, History and Retention Errors</v>
+      </c>
+      <c r="C104" s="2" t="str">
+        <f>'Databricks Master Syllabus'!A100</f>
+        <v>13. Production, Troubleshooting &amp; Capstone</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E104" s="2">
+        <v>0</v>
+      </c>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+    </row>
+    <row r="105" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A105" s="3">
+        <v>100</v>
+      </c>
+      <c r="B105" s="3" t="str">
+        <f>'Databricks Master Syllabus'!C101</f>
+        <v>Query Profile and Query History</v>
+      </c>
+      <c r="C105" s="3" t="str">
+        <f>'Databricks Master Syllabus'!A101</f>
+        <v>13. Production, Troubleshooting &amp; Capstone</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E105" s="3">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+    </row>
+    <row r="106" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A106" s="2">
+        <v>101</v>
+      </c>
+      <c r="B106" s="2" t="str">
+        <f>'Databricks Master Syllabus'!C102</f>
+        <v>Compute That Won't Start</v>
+      </c>
+      <c r="C106" s="2" t="str">
+        <f>'Databricks Master Syllabus'!A102</f>
+        <v>13. Production, Troubleshooting &amp; Capstone</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E106" s="2">
+        <v>0</v>
+      </c>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+    </row>
+    <row r="107" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A107" s="3">
+        <v>102</v>
+      </c>
+      <c r="B107" s="3" t="str">
+        <f>'Databricks Master Syllabus'!C103</f>
+        <v>Libraries and Init Scripts</v>
+      </c>
+      <c r="C107" s="3" t="str">
+        <f>'Databricks Master Syllabus'!A103</f>
+        <v>13. Production, Troubleshooting &amp; Capstone</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E107" s="3">
+        <v>0</v>
+      </c>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+    </row>
+    <row r="108" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A108" s="2">
+        <v>103</v>
+      </c>
+      <c r="B108" s="2" t="str">
+        <f>'Databricks Master Syllabus'!C104</f>
+        <v>Runtime Lifecycle and Upgrades</v>
+      </c>
+      <c r="C108" s="2" t="str">
+        <f>'Databricks Master Syllabus'!A104</f>
+        <v>13. Production, Troubleshooting &amp; Capstone</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E108" s="2">
+        <v>0</v>
+      </c>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
+    </row>
+    <row r="109" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A109" s="3">
+        <v>104</v>
+      </c>
+      <c r="B109" s="3" t="str">
+        <f>'Databricks Master Syllabus'!C105</f>
+        <v>Environment Isolation and Catalog Strategy</v>
+      </c>
+      <c r="C109" s="3" t="str">
+        <f>'Databricks Master Syllabus'!A105</f>
+        <v>13. Production, Troubleshooting &amp; Capstone</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E109" s="3">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+    </row>
+    <row r="110" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A110" s="2">
+        <v>105</v>
+      </c>
+      <c r="B110" s="2" t="str">
+        <f>'Databricks Master Syllabus'!C106</f>
+        <v>Encryption and Customer-Managed Keys</v>
+      </c>
+      <c r="C110" s="2" t="str">
+        <f>'Databricks Master Syllabus'!A106</f>
+        <v>13. Production, Troubleshooting &amp; Capstone</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E110" s="2">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+    </row>
+    <row r="111" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A111" s="3">
+        <v>106</v>
+      </c>
+      <c r="B111" s="3" t="str">
+        <f>'Databricks Master Syllabus'!C107</f>
+        <v>High Availability and Disaster Recovery</v>
+      </c>
+      <c r="C111" s="3" t="str">
+        <f>'Databricks Master Syllabus'!A107</f>
+        <v>13. Production, Troubleshooting &amp; Capstone</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E111" s="3">
+        <v>0</v>
+      </c>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+    </row>
+    <row r="112" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A112" s="2">
+        <v>107</v>
+      </c>
+      <c r="B112" s="2" t="str">
+        <f>'Databricks Master Syllabus'!C108</f>
+        <v>Testing Databricks Code</v>
+      </c>
+      <c r="C112" s="2" t="str">
+        <f>'Databricks Master Syllabus'!A108</f>
+        <v>13. Production, Troubleshooting &amp; Capstone</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E112" s="2">
+        <v>0</v>
+      </c>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
+    </row>
+    <row r="113" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+      <c r="A113" s="3">
+        <v>108</v>
+      </c>
+      <c r="B113" s="3" t="str">
+        <f>'Databricks Master Syllabus'!C109</f>
+        <v>Capstone: End-to-End Medallion Pipeline</v>
+      </c>
+      <c r="C113" s="3" t="str">
+        <f>'Databricks Master Syllabus'!A109</f>
+        <v>13. Production, Troubleshooting &amp; Capstone</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E113" s="3">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
+      <c r="H113" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6235,178 +7673,178 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>428</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>360</v>
+        <v>429</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>361</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>362</v>
+        <v>431</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>363</v>
+        <v>432</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>364</v>
+        <v>433</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>365</v>
+        <v>434</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>366</v>
+        <v>435</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>367</v>
+        <v>436</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>368</v>
+        <v>437</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>369</v>
+        <v>438</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>370</v>
+        <v>439</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>371</v>
+        <v>440</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>372</v>
+        <v>441</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>373</v>
+        <v>442</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>374</v>
+        <v>443</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>375</v>
+        <v>444</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>377</v>
+        <v>446</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>378</v>
+        <v>447</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>379</v>
+        <v>448</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>380</v>
+        <v>449</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>381</v>
+        <v>450</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>382</v>
+        <v>451</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>383</v>
+        <v>452</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>384</v>
+        <v>453</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>385</v>
+        <v>454</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>386</v>
+        <v>455</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>387</v>
+        <v>456</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>388</v>
+        <v>457</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>389</v>
+        <v>458</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>390</v>
+        <v>459</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>391</v>
+        <v>460</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>392</v>
+        <v>461</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>393</v>
+        <v>462</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>394</v>
+        <v>463</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>392</v>
+        <v>461</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>395</v>
+        <v>464</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>396</v>
+        <v>465</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>397</v>
+        <v>466</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>398</v>
+        <v>467</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>399</v>
+        <v>468</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>400</v>
+        <v>469</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>401</v>
+        <v>470</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>402</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -6425,66 +7863,66 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>403</v>
+        <v>472</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>404</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>405</v>
+        <v>474</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>406</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>407</v>
+        <v>476</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>408</v>
+        <v>477</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>409</v>
+        <v>478</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>410</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>411</v>
+        <v>480</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>412</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>414</v>
+        <v>483</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>415</v>
+        <v>484</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>416</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>417</v>
+        <v>486</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>418</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="28" x14ac:dyDescent="0.35">
@@ -6492,63 +7930,583 @@
         <v>102</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>419</v>
+        <v>488</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>371</v>
+        <v>440</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>420</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>421</v>
+        <v>490</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>422</v>
+        <v>491</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>423</v>
+        <v>492</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>424</v>
+        <v>493</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>425</v>
+        <v>494</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>426</v>
+        <v>495</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>427</v>
+        <v>496</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>428</v>
+        <v>497</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>429</v>
+        <v>498</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>430</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>431</v>
+        <v>500</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>432</v>
+        <v>501</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:D36"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="3" width="70" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>639</v>
       </c>
     </row>
   </sheetData>

--- a/docs/research/Databricks_Data_Engineering_Mastery_Roadmap.xlsx
+++ b/docs/research/Databricks_Data_Engineering_Mastery_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\PrepBench\.claude\worktrees\databricks-research-1e243f\docs\research\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4230A312-1C88-4DD3-BD53-B23662758D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6328D6D0-0052-413C-AE5B-E3F1F747CDD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -219,7 +219,7 @@
     <t>Understand Delta Lake as Parquet data files plus a file-based transaction log, and that every Databricks table is Delta by default.</t>
   </si>
   <si>
-    <t>Create a Delta table, list its directory, and point out the data files and the _delta_log folder.</t>
+    <t>Create a Delta table and use DESCRIBE DETAIL to show its location, file count and protocol, then explain what its _delta_log folder holds.</t>
   </si>
   <si>
     <t>§2.1</t>
@@ -231,7 +231,7 @@
     <t>Master the log: one JSON file per version, 20-digit zero-padded names, contiguous versions, a version's file as the unit of atomicity.</t>
   </si>
   <si>
-    <t>Make three writes, open the three JSON commits, and name the version each one created.</t>
+    <t>Make three writes, list them with DESCRIBE HISTORY, and name the version and JSON commit file each one created.</t>
   </si>
   <si>
     <t>Log Actions</t>
@@ -2686,7 +2686,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="28" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="42" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>57</v>
       </c>
